--- a/outputs/01a0f354-50a1-7850-9a3e-c4f75b90728b/ConvertTable配方.xlsx
+++ b/outputs/01a0f354-50a1-7850-9a3e-c4f75b90728b/ConvertTable配方.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方总览" sheetId="1" r:id="Rad39255c93f344f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通转换" sheetId="2" r:id="R834b4070254d42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幽匿进阶" sheetId="3" r:id="R5f9f05475a754705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触媒增殖" sheetId="4" r:id="Rec211c1d596b41c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方块合成" sheetId="5" r:id="R4541d6a377f44fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方总览" sheetId="1" r:id="R2d0bef3ee8964282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通转换" sheetId="2" r:id="Raf842d6e706e4963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幽匿进阶" sheetId="3" r:id="Ra15cc80006f947f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触媒增殖" sheetId="4" r:id="Rb60f3c7768c94b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方块合成" sheetId="5" r:id="R4b6fe9a8422e494c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.00%"/>
+    <x:numFmt numFmtId="202" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -77,6 +79,12 @@
       <x:color rgb="FF374151"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF374151"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="8">
     <x:fill>
@@ -127,7 +135,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -215,6 +223,24 @@
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -245,8 +271,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recipes2" displayName="Recipes2" ref="A6:R89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:R89"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recipes2" displayName="Recipes2" ref="A6:R124" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:R124"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="配方 ID"/>
     <x:tableColumn id="2" name="配方"/>
@@ -272,9 +298,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Recipes3" displayName="Recipes3" ref="A6:G111" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:G111"/>
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Recipes3" displayName="Recipes3" ref="A6:J111" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:J111"/>
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="分类"/>
     <x:tableColumn id="2" name="触媒（不消耗）"/>
     <x:tableColumn id="3" name="产物"/>
@@ -282,6 +308,9 @@
     <x:tableColumn id="5" name="配方 ID"/>
     <x:tableColumn id="6" name="触媒 ID"/>
     <x:tableColumn id="7" name="产物 ID"/>
+    <x:tableColumn id="8" name="源本（不消耗）"/>
+    <x:tableColumn id="9" name="源本数量"/>
+    <x:tableColumn id="10" name="源本 ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -503,11 +532,19 @@
     <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="74" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="35" t="str">
-        <x:v>ConvertTable v0.2.0 配方</x:v>
+        <x:v>ConvertTable v0.3.1 配方</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -559,8 +596,8 @@
         <x:v>幽匿进阶配方</x:v>
       </x:c>
       <x:c r="B8" s="38" t="n">
-        <x:f>COUNTA('幽匿进阶'!A7:A89)</x:f>
-        <x:v>83</x:v>
+        <x:f>COUNTA('幽匿进阶'!A7:A124)</x:f>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
         <x:v>幽匿进阶：主材、催化、可用灵魂、相位、返还</x:v>
@@ -642,10 +679,10 @@
         <x:v>幽匿</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>普通每批消耗 1 个可用灵魂；进阶按配方消耗可用灵魂，均不消耗相位。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="30" customHeight="1">
+        <x:v>普通每批消耗 3 个可用灵魂；进阶按配方消耗可用灵魂，均不消耗相位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="7" t="str">
         <x:v>使用要点</x:v>
       </x:c>
@@ -653,7 +690,7 @@
         <x:v>增殖</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
-        <x:v>触媒永不消耗；界面显示当前产速和下一件进度；每条晶脉只接一座增殖台。</x:v>
+        <x:v>触媒＋一件目标物品作源本，两者保留。晶脉没有范围、节点、母岩或总产速上限；多个增殖台共用供给。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
@@ -665,6 +702,197 @@
       </x:c>
       <x:c r="C19" s="8" t="str">
         <x:v>合格死亡的 1 XP = 32 灵魂；0 XP 不提供；默认无需玩家击杀；每台上限 4096。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="39" t="str">
+        <x:v>钓鱼材料</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="41" t="str">
+        <x:v>材料</x:v>
+      </x:c>
+      <x:c r="B22" s="41" t="str">
+        <x:v>获取池</x:v>
+      </x:c>
+      <x:c r="C22" s="41" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="D22" s="41" t="str">
+        <x:v>追加权重</x:v>
+      </x:c>
+      <x:c r="E22" s="41" t="str">
+        <x:v>参考钓获概率</x:v>
+      </x:c>
+      <x:c r="F22" s="41" t="str">
+        <x:v>最少数量</x:v>
+      </x:c>
+      <x:c r="G22" s="41" t="str">
+        <x:v>最多数量</x:v>
+      </x:c>
+      <x:c r="I22" s="2" t="str">
+        <x:v>原版参考</x:v>
+      </x:c>
+      <x:c r="J22" s="2" t="str">
+        <x:v>分类概率</x:v>
+      </x:c>
+      <x:c r="K22" s="2" t="str">
+        <x:v>原分类权重</x:v>
+      </x:c>
+      <x:c r="L22" s="2" t="str">
+        <x:v>追加后总权重</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>鱼类</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>陆栖、飞行及自然生命；远古种子抽卡</x:v>
+      </x:c>
+      <x:c r="D23" s="43" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E23" s="44" t="n">
+        <x:f>$J$23*D23/$L$23</x:f>
+        <x:v>0.056666666666666664</x:v>
+      </x:c>
+      <x:c r="F23" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="2" t="str">
+        <x:v>鱼类</x:v>
+      </x:c>
+      <x:c r="J23" s="45" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="K23" s="46" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L23" s="46" t="n">
+        <x:f>K23+SUMIFS(D23:D27,B23:B27,I23)</x:f>
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>鱼类</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>水栖生命塑形</x:v>
+      </x:c>
+      <x:c r="D24" s="43" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E24" s="44" t="n">
+        <x:f>$J$23*D24/$L$23</x:f>
+        <x:v>0.042499999999999996</x:v>
+      </x:c>
+      <x:c r="F24" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" s="2" t="str">
+        <x:v>宝藏</x:v>
+      </x:c>
+      <x:c r="J24" s="45" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="K24" s="46" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L24" s="46" t="n">
+        <x:f>K24+SUMIFS(D23:D27,B23:B27,I24)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="8" t="str">
+        <x:v>Unbroken Cognizance</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>鱼类</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>村民与流浪商人塑形</x:v>
+      </x:c>
+      <x:c r="D25" s="43" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="44" t="n">
+        <x:f>$J$23*D25/$L$23</x:f>
+        <x:v>0.014166666666666666</x:v>
+      </x:c>
+      <x:c r="F25" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="8" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>鱼类</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str">
+        <x:v>灵异、亡灵与构造生命塑形</x:v>
+      </x:c>
+      <x:c r="D26" s="43" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E26" s="44" t="n">
+        <x:f>$J$23*D26/$L$23</x:f>
+        <x:v>0.028333333333333332</x:v>
+      </x:c>
+      <x:c r="F26" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="48" customHeight="1">
+      <x:c r="A27" s="8" t="str">
+        <x:v>紫水晶碎片</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>宝藏</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>自然材料增殖的触媒；其他紫水晶用途</x:v>
+      </x:c>
+      <x:c r="D27" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="44" t="n">
+        <x:f>$J$24*D27/$L$24</x:f>
+        <x:v>0.0071428571428571435</x:v>
+      </x:c>
+      <x:c r="F27" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="43" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="3" t="str">
+        <x:v>概率按原版开放水域、无海眷计算；附魔和其他模组可改变实际钓获比例。宝藏仍受开放水域条件约束。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -788,7 +1016,7 @@
       <x:c r="G7" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H7" s="15" t="n">
         <x:v>13</x:v>
@@ -834,7 +1062,7 @@
       <x:c r="G8" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H8" s="16" t="n">
         <x:v>13</x:v>
@@ -880,7 +1108,7 @@
       <x:c r="G9" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H9" s="15" t="n">
         <x:v>13</x:v>
@@ -926,7 +1154,7 @@
       <x:c r="G10" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H10" s="16" t="n">
         <x:v>13</x:v>
@@ -972,7 +1200,7 @@
       <x:c r="G11" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H11" s="15" t="n">
         <x:v>13</x:v>
@@ -1018,7 +1246,7 @@
       <x:c r="G12" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H12" s="16" t="n">
         <x:v>13</x:v>
@@ -1064,7 +1292,7 @@
       <x:c r="G13" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H13" s="15" t="n">
         <x:v>13</x:v>
@@ -1110,7 +1338,7 @@
       <x:c r="G14" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H14" s="16" t="n">
         <x:v>13</x:v>
@@ -1156,7 +1384,7 @@
       <x:c r="G15" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H15" s="15" t="n">
         <x:v>13</x:v>
@@ -1202,7 +1430,7 @@
       <x:c r="G16" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H16" s="16" t="n">
         <x:v>13</x:v>
@@ -1248,7 +1476,7 @@
       <x:c r="G17" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H17" s="15" t="n">
         <x:v>13</x:v>
@@ -1295,7 +1523,7 @@
       <x:c r="G18" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H18" s="16" t="n">
         <x:v>13</x:v>
@@ -1341,7 +1569,7 @@
       <x:c r="G19" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H19" s="15" t="n">
         <x:v>13</x:v>
@@ -1387,7 +1615,7 @@
       <x:c r="G20" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H20" s="16" t="n">
         <x:v>13</x:v>
@@ -1433,7 +1661,7 @@
       <x:c r="G21" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H21" s="15" t="n">
         <x:v>12</x:v>
@@ -1478,7 +1706,7 @@
       <x:c r="G22" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H22" s="16" t="n">
         <x:v>12</x:v>
@@ -1523,7 +1751,7 @@
       <x:c r="G23" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H23" s="15" t="n">
         <x:v>14</x:v>
@@ -1569,7 +1797,7 @@
       <x:c r="G24" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H24" s="16" t="n">
         <x:v>19</x:v>
@@ -1616,7 +1844,7 @@
       <x:c r="G25" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H25" s="15" t="n">
         <x:v>19</x:v>
@@ -1663,7 +1891,7 @@
       <x:c r="G26" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H26" s="16" t="n">
         <x:v>15</x:v>
@@ -1709,7 +1937,7 @@
       <x:c r="G27" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H27" s="15" t="n">
         <x:v>11</x:v>
@@ -1754,7 +1982,7 @@
       <x:c r="G28" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H28" s="16" t="n">
         <x:v>2</x:v>
@@ -1797,7 +2025,7 @@
       <x:c r="G29" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H29" s="15" t="n">
         <x:v>42</x:v>
@@ -1850,7 +2078,7 @@
       <x:c r="G30" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H30" s="16" t="n">
         <x:v>45</x:v>
@@ -1904,7 +2132,7 @@
       <x:c r="G31" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H31" s="15" t="n">
         <x:v>32</x:v>
@@ -1954,7 +2182,7 @@
       <x:c r="G32" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H32" s="16" t="n">
         <x:v>2</x:v>
@@ -1997,7 +2225,7 @@
       <x:c r="G33" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H33" s="15" t="n">
         <x:v>2</x:v>
@@ -2040,7 +2268,7 @@
       <x:c r="G34" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H34" s="16" t="n">
         <x:v>16</x:v>
@@ -2086,7 +2314,7 @@
       <x:c r="G35" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H35" s="15" t="n">
         <x:v>16</x:v>
@@ -2132,7 +2360,7 @@
       <x:c r="G36" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H36" s="16" t="n">
         <x:v>16</x:v>
@@ -2178,7 +2406,7 @@
       <x:c r="G37" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H37" s="15" t="n">
         <x:v>16</x:v>
@@ -2225,7 +2453,7 @@
       <x:c r="G38" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H38" s="16" t="n">
         <x:v>17</x:v>
@@ -2272,7 +2500,7 @@
       <x:c r="G39" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H39" s="15" t="n">
         <x:v>16</x:v>
@@ -2318,7 +2546,7 @@
       <x:c r="G40" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H40" s="16" t="n">
         <x:v>17</x:v>
@@ -2365,7 +2593,7 @@
       <x:c r="G41" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H41" s="15" t="n">
         <x:v>17</x:v>
@@ -2412,7 +2640,7 @@
       <x:c r="G42" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H42" s="16" t="n">
         <x:v>17</x:v>
@@ -2459,7 +2687,7 @@
       <x:c r="G43" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H43" s="15" t="n">
         <x:v>16</x:v>
@@ -2505,7 +2733,7 @@
       <x:c r="G44" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H44" s="16" t="n">
         <x:v>16</x:v>
@@ -2550,7 +2778,7 @@
       </x:c>
       <x:c r="G45" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H45" s="15" t="n">
         <x:v>17</x:v>
@@ -2595,7 +2823,7 @@
       <x:c r="G46" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H46" s="16" t="n">
         <x:v>4</x:v>
@@ -2638,7 +2866,7 @@
       <x:c r="G47" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H47" s="15" t="n">
         <x:v>4</x:v>
@@ -2681,7 +2909,7 @@
       <x:c r="G48" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H48" s="16" t="n">
         <x:v>4</x:v>
@@ -2724,7 +2952,7 @@
       <x:c r="G49" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H49" s="15" t="n">
         <x:v>4</x:v>
@@ -2768,7 +2996,7 @@
       <x:c r="G50" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H50" s="16" t="n">
         <x:v>4</x:v>
@@ -2811,7 +3039,7 @@
       <x:c r="G51" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H51" s="15" t="n">
         <x:v>4</x:v>
@@ -2855,7 +3083,7 @@
       <x:c r="G52" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H52" s="16" t="n">
         <x:v>4</x:v>
@@ -2898,7 +3126,7 @@
       <x:c r="G53" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H53" s="15" t="n">
         <x:v>4</x:v>
@@ -2942,7 +3170,7 @@
       <x:c r="G54" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H54" s="16" t="n">
         <x:v>4</x:v>
@@ -2985,7 +3213,7 @@
       <x:c r="G55" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H55" s="15" t="n">
         <x:v>4</x:v>
@@ -3029,7 +3257,7 @@
       <x:c r="G56" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H56" s="16" t="n">
         <x:v>4</x:v>
@@ -3072,7 +3300,7 @@
       <x:c r="G57" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H57" s="15" t="n">
         <x:v>4</x:v>
@@ -3116,7 +3344,7 @@
       <x:c r="G58" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H58" s="16" t="n">
         <x:v>4</x:v>
@@ -3159,7 +3387,7 @@
       <x:c r="G59" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H59" s="15" t="n">
         <x:v>4</x:v>
@@ -3202,7 +3430,7 @@
       <x:c r="G60" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H60" s="16" t="n">
         <x:v>4</x:v>
@@ -3245,7 +3473,7 @@
       <x:c r="G61" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H61" s="15" t="n">
         <x:v>4</x:v>
@@ -3288,7 +3516,7 @@
       <x:c r="G62" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H62" s="16" t="n">
         <x:v>4</x:v>
@@ -3331,7 +3559,7 @@
       <x:c r="G63" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H63" s="15" t="n">
         <x:v>4</x:v>
@@ -3375,7 +3603,7 @@
       <x:c r="G64" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H64" s="16" t="n">
         <x:v>4</x:v>
@@ -3418,7 +3646,7 @@
       <x:c r="G65" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H65" s="15" t="n">
         <x:v>4</x:v>
@@ -3462,7 +3690,7 @@
       <x:c r="G66" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H66" s="16" t="n">
         <x:v>4</x:v>
@@ -3505,7 +3733,7 @@
       <x:c r="G67" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H67" s="15" t="n">
         <x:v>4</x:v>
@@ -3548,7 +3776,7 @@
       <x:c r="G68" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H68" s="16" t="n">
         <x:v>4</x:v>
@@ -3591,7 +3819,7 @@
       <x:c r="G69" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H69" s="15" t="n">
         <x:v>4</x:v>
@@ -3635,7 +3863,7 @@
       <x:c r="G70" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H70" s="16" t="n">
         <x:v>4</x:v>
@@ -3678,7 +3906,7 @@
       <x:c r="G71" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H71" s="15" t="n">
         <x:v>4</x:v>
@@ -3722,7 +3950,7 @@
       <x:c r="G72" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H72" s="16" t="n">
         <x:v>4</x:v>
@@ -3765,7 +3993,7 @@
       <x:c r="G73" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H73" s="15" t="n">
         <x:v>4</x:v>
@@ -3809,7 +4037,7 @@
       <x:c r="G74" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H74" s="16" t="n">
         <x:v>4</x:v>
@@ -3852,7 +4080,7 @@
       <x:c r="G75" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H75" s="15" t="n">
         <x:v>4</x:v>
@@ -3896,7 +4124,7 @@
       <x:c r="G76" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H76" s="16" t="n">
         <x:v>2</x:v>
@@ -3938,7 +4166,7 @@
       </x:c>
       <x:c r="G77" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H77" s="15" t="n">
         <x:v>7</x:v>
@@ -3979,7 +4207,7 @@
       </x:c>
       <x:c r="G78" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H78" s="16" t="n">
         <x:v>3</x:v>
@@ -4019,7 +4247,7 @@
       </x:c>
       <x:c r="G79" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H79" s="15" t="n">
         <x:v>2</x:v>
@@ -4059,7 +4287,7 @@
       </x:c>
       <x:c r="G80" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H80" s="16" t="n">
         <x:v>2</x:v>
@@ -4100,7 +4328,7 @@
       <x:c r="G81" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H81" s="15" t="n">
         <x:v>2</x:v>
@@ -4143,7 +4371,7 @@
       <x:c r="G82" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H82" s="16" t="n">
         <x:v>2</x:v>
@@ -4186,7 +4414,7 @@
       <x:c r="G83" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H83" s="15" t="n">
         <x:v>2</x:v>
@@ -4228,7 +4456,7 @@
       </x:c>
       <x:c r="G84" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H84" s="16" t="n">
         <x:v>5</x:v>
@@ -4269,7 +4497,7 @@
       </x:c>
       <x:c r="G85" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H85" s="15" t="n">
         <x:v>5</x:v>
@@ -4310,7 +4538,7 @@
       </x:c>
       <x:c r="G86" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H86" s="16" t="n">
         <x:v>5</x:v>
@@ -4351,7 +4579,7 @@
       </x:c>
       <x:c r="G87" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H87" s="15" t="n">
         <x:v>5</x:v>
@@ -4392,7 +4620,7 @@
       </x:c>
       <x:c r="G88" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H88" s="16" t="n">
         <x:v>5</x:v>
@@ -4433,7 +4661,7 @@
       </x:c>
       <x:c r="G89" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H89" s="15" t="n">
         <x:v>5</x:v>
@@ -4474,7 +4702,7 @@
       </x:c>
       <x:c r="G90" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H90" s="16" t="n">
         <x:v>14</x:v>
@@ -4517,7 +4745,7 @@
       </x:c>
       <x:c r="G91" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H91" s="15" t="n">
         <x:v>5</x:v>
@@ -4558,7 +4786,7 @@
       </x:c>
       <x:c r="G92" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H92" s="16" t="n">
         <x:v>7</x:v>
@@ -4599,7 +4827,7 @@
       </x:c>
       <x:c r="G93" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H93" s="15" t="n">
         <x:v>3</x:v>
@@ -4639,7 +4867,7 @@
       </x:c>
       <x:c r="G94" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H94" s="16" t="n">
         <x:v>4</x:v>
@@ -4679,7 +4907,7 @@
       </x:c>
       <x:c r="G95" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H95" s="15" t="n">
         <x:v>2</x:v>
@@ -4719,7 +4947,7 @@
       </x:c>
       <x:c r="G96" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H96" s="16" t="n">
         <x:v>6</x:v>
@@ -4760,7 +4988,7 @@
       </x:c>
       <x:c r="G97" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H97" s="15" t="n">
         <x:v>3</x:v>
@@ -4800,7 +5028,7 @@
       </x:c>
       <x:c r="G98" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H98" s="16" t="n">
         <x:v>2</x:v>
@@ -4840,7 +5068,7 @@
       </x:c>
       <x:c r="G99" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H99" s="15" t="n">
         <x:v>2</x:v>
@@ -4881,7 +5109,7 @@
       <x:c r="G100" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H100" s="16" t="n">
         <x:v>16</x:v>
@@ -4927,7 +5155,7 @@
       <x:c r="G101" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H101" s="15" t="n">
         <x:v>16</x:v>
@@ -4973,7 +5201,7 @@
       <x:c r="G102" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H102" s="16" t="n">
         <x:v>16</x:v>
@@ -5020,7 +5248,7 @@
       <x:c r="G103" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H103" s="15" t="n">
         <x:v>16</x:v>
@@ -5067,7 +5295,7 @@
       <x:c r="G104" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H104" s="16" t="n">
         <x:v>16</x:v>
@@ -5113,7 +5341,7 @@
       <x:c r="G105" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H105" s="15" t="n">
         <x:v>3</x:v>
@@ -5156,7 +5384,7 @@
       <x:c r="G106" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H106" s="16" t="n">
         <x:v>4</x:v>
@@ -5199,7 +5427,7 @@
       <x:c r="G107" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H107" s="15" t="n">
         <x:v>2</x:v>
@@ -5241,7 +5469,7 @@
       </x:c>
       <x:c r="G108" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H108" s="16" t="n">
         <x:v>4</x:v>
@@ -5281,7 +5509,7 @@
       </x:c>
       <x:c r="G109" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H109" s="15" t="n">
         <x:v>4</x:v>
@@ -5322,7 +5550,7 @@
       <x:c r="G110" s="12" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H110" s="16" t="n">
         <x:v>2</x:v>
@@ -5365,7 +5593,7 @@
       <x:c r="G111" s="8" t="str">
         <x:v>黑金：1 金粒
 末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H111" s="15" t="n">
         <x:v>2</x:v>
@@ -5407,7 +5635,7 @@
       </x:c>
       <x:c r="G112" s="12" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H112" s="16" t="n">
         <x:v>2</x:v>
@@ -5447,7 +5675,7 @@
       </x:c>
       <x:c r="G113" s="8" t="str">
         <x:v>末地：1 相位
-幽匿：1 可用灵魂</x:v>
+幽匿：3 可用灵魂</x:v>
       </x:c>
       <x:c r="H113" s="15" t="n">
         <x:v>2</x:v>
@@ -5469,7 +5697,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55965cd8cc414524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab708fb60ef44d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5617,7 +5845,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J7" s="15" t="n">
-        <x:v>32</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K7" s="15" t="n">
         <x:v>0</x:v>
@@ -5671,7 +5899,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>0</x:v>
@@ -5725,7 +5953,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K9" s="15" t="n">
         <x:v>0</x:v>
@@ -5779,7 +6007,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:v>0</x:v>
@@ -5833,7 +6061,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K11" s="15" t="n">
         <x:v>0</x:v>
@@ -5887,7 +6115,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="16" t="n">
         <x:v>0</x:v>
@@ -5941,7 +6169,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="15" t="n">
         <x:v>0</x:v>
@@ -5997,7 +6225,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K14" s="16" t="n">
         <x:v>0</x:v>
@@ -6053,7 +6281,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K15" s="15" t="n">
         <x:v>0</x:v>
@@ -6109,7 +6337,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K16" s="16" t="n">
         <x:v>0</x:v>
@@ -6165,7 +6393,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K17" s="15" t="n">
         <x:v>0</x:v>
@@ -6221,7 +6449,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K18" s="16" t="n">
         <x:v>0</x:v>
@@ -6277,7 +6505,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K19" s="15" t="n">
         <x:v>0</x:v>
@@ -6333,7 +6561,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K20" s="16" t="n">
         <x:v>0</x:v>
@@ -6389,7 +6617,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K21" s="15" t="n">
         <x:v>0</x:v>
@@ -6445,7 +6673,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K22" s="16" t="n">
         <x:v>0</x:v>
@@ -6501,7 +6729,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K23" s="15" t="n">
         <x:v>0</x:v>
@@ -6557,7 +6785,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K24" s="16" t="n">
         <x:v>0</x:v>
@@ -6613,7 +6841,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J25" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K25" s="15" t="n">
         <x:v>0</x:v>
@@ -6669,7 +6897,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K26" s="16" t="n">
         <x:v>0</x:v>
@@ -6725,7 +6953,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J27" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K27" s="15" t="n">
         <x:v>0</x:v>
@@ -6781,7 +7009,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K28" s="16" t="n">
         <x:v>0</x:v>
@@ -6837,7 +7065,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J29" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K29" s="15" t="n">
         <x:v>0</x:v>
@@ -6893,7 +7121,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K30" s="16" t="n">
         <x:v>0</x:v>
@@ -6947,7 +7175,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J31" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K31" s="15" t="n">
         <x:v>0</x:v>
@@ -7003,7 +7231,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J32" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K32" s="16" t="n">
         <x:v>0</x:v>
@@ -7059,7 +7287,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J33" s="15" t="n">
-        <x:v>64</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K33" s="15" t="n">
         <x:v>0</x:v>
@@ -7115,7 +7343,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J34" s="16" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K34" s="16" t="n">
         <x:v>0</x:v>
@@ -7150,16 +7378,16 @@
         <x:v>鸡刷怪蛋</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D35" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E35" s="8" t="str">
-        <x:v>羽毛</x:v>
+        <x:v>小麦种子</x:v>
       </x:c>
       <x:c r="F35" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>鸡刷怪蛋</x:v>
@@ -7171,7 +7399,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J35" s="15" t="n">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K35" s="15" t="n">
         <x:v>0</x:v>
@@ -7186,10 +7414,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O35" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P35" s="8" t="str">
-        <x:v>minecraft:feather</x:v>
+        <x:v>minecraft:wheat_seeds</x:v>
       </x:c>
       <x:c r="Q35" s="8" t="str">
         <x:v>minecraft:chicken_spawn_egg</x:v>
@@ -7206,16 +7434,16 @@
         <x:v>牛刷怪蛋</x:v>
       </x:c>
       <x:c r="C36" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D36" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
-        <x:v>皮革</x:v>
+        <x:v>小麦</x:v>
       </x:c>
       <x:c r="F36" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G36" s="12" t="str">
         <x:v>牛刷怪蛋</x:v>
@@ -7227,7 +7455,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J36" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K36" s="16" t="n">
         <x:v>0</x:v>
@@ -7242,10 +7470,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O36" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P36" s="12" t="str">
-        <x:v>minecraft:leather</x:v>
+        <x:v>minecraft:wheat</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="str">
         <x:v>minecraft:cow_spawn_egg</x:v>
@@ -7262,16 +7490,16 @@
         <x:v>猪刷怪蛋</x:v>
       </x:c>
       <x:c r="C37" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D37" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="8" t="str">
-        <x:v>生猪排</x:v>
+        <x:v>胡萝卜</x:v>
       </x:c>
       <x:c r="F37" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>猪刷怪蛋</x:v>
@@ -7283,7 +7511,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J37" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K37" s="15" t="n">
         <x:v>0</x:v>
@@ -7298,10 +7526,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O37" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P37" s="8" t="str">
-        <x:v>minecraft:porkchop</x:v>
+        <x:v>minecraft:carrot</x:v>
       </x:c>
       <x:c r="Q37" s="8" t="str">
         <x:v>minecraft:pig_spawn_egg</x:v>
@@ -7318,16 +7546,16 @@
         <x:v>羊刷怪蛋</x:v>
       </x:c>
       <x:c r="C38" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D38" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="12" t="str">
-        <x:v>白色羊毛</x:v>
+        <x:v>小麦</x:v>
       </x:c>
       <x:c r="F38" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G38" s="12" t="str">
         <x:v>绵羊刷怪蛋</x:v>
@@ -7339,7 +7567,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J38" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K38" s="16" t="n">
         <x:v>0</x:v>
@@ -7354,10 +7582,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O38" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P38" s="12" t="str">
-        <x:v>minecraft:white_wool</x:v>
+        <x:v>minecraft:wheat</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="str">
         <x:v>minecraft:sheep_spawn_egg</x:v>
@@ -7374,16 +7602,16 @@
         <x:v>兔刷怪蛋</x:v>
       </x:c>
       <x:c r="C39" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D39" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E39" s="8" t="str">
-        <x:v>兔子皮</x:v>
+        <x:v>蒲公英</x:v>
       </x:c>
       <x:c r="F39" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>兔子刷怪蛋</x:v>
@@ -7395,7 +7623,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J39" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K39" s="15" t="n">
         <x:v>0</x:v>
@@ -7410,10 +7638,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O39" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P39" s="8" t="str">
-        <x:v>minecraft:rabbit_hide</x:v>
+        <x:v>minecraft:dandelion</x:v>
       </x:c>
       <x:c r="Q39" s="8" t="str">
         <x:v>minecraft:rabbit_spawn_egg</x:v>
@@ -7430,13 +7658,13 @@
         <x:v>蜜蜂刷怪蛋</x:v>
       </x:c>
       <x:c r="C40" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D40" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E40" s="12" t="str">
-        <x:v>蜜脾</x:v>
+        <x:v>盛开的杜鹃花丛</x:v>
       </x:c>
       <x:c r="F40" s="16" t="n">
         <x:v>8</x:v>
@@ -7451,7 +7679,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J40" s="16" t="n">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K40" s="16" t="n">
         <x:v>0</x:v>
@@ -7466,10 +7694,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O40" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P40" s="12" t="str">
-        <x:v>minecraft:honeycomb</x:v>
+        <x:v>minecraft:flowering_azalea</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="str">
         <x:v>minecraft:bee_spawn_egg</x:v>
@@ -7486,7 +7714,7 @@
         <x:v>青蛙刷怪蛋</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D41" s="15" t="n">
         <x:v>1</x:v>
@@ -7507,7 +7735,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J41" s="15" t="n">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K41" s="15" t="n">
         <x:v>0</x:v>
@@ -7522,7 +7750,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O41" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P41" s="8" t="str">
         <x:v>minecraft:slime_ball</x:v>
@@ -7542,16 +7770,16 @@
         <x:v>海龟刷怪蛋</x:v>
       </x:c>
       <x:c r="C42" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Stillwater Palimpsest</x:v>
       </x:c>
       <x:c r="D42" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="12" t="str">
-        <x:v>海龟鳞甲</x:v>
+        <x:v>海草</x:v>
       </x:c>
       <x:c r="F42" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G42" s="12" t="str">
         <x:v>海龟刷怪蛋</x:v>
@@ -7563,7 +7791,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J42" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K42" s="16" t="n">
         <x:v>0</x:v>
@@ -7578,10 +7806,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O42" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:stillwater_palimpsest</x:v>
       </x:c>
       <x:c r="P42" s="12" t="str">
-        <x:v>minecraft:turtle_scute</x:v>
+        <x:v>minecraft:seagrass</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="str">
         <x:v>minecraft:turtle_spawn_egg</x:v>
@@ -7598,16 +7826,16 @@
         <x:v>山羊刷怪蛋</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D43" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E43" s="8" t="str">
-        <x:v>山羊角</x:v>
+        <x:v>干草捆</x:v>
       </x:c>
       <x:c r="F43" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>山羊刷怪蛋</x:v>
@@ -7619,7 +7847,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J43" s="15" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K43" s="15" t="n">
         <x:v>0</x:v>
@@ -7634,10 +7862,10 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O43" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P43" s="8" t="str">
-        <x:v>minecraft:goat_horn</x:v>
+        <x:v>minecraft:hay_block</x:v>
       </x:c>
       <x:c r="Q43" s="8" t="str">
         <x:v>minecraft:goat_spawn_egg</x:v>
@@ -7654,7 +7882,7 @@
         <x:v>骆驼刷怪蛋</x:v>
       </x:c>
       <x:c r="C44" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D44" s="16" t="n">
         <x:v>1</x:v>
@@ -7675,7 +7903,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J44" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K44" s="16" t="n">
         <x:v>0</x:v>
@@ -7690,7 +7918,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O44" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P44" s="12" t="str">
         <x:v>minecraft:cactus</x:v>
@@ -7710,7 +7938,7 @@
         <x:v>狼刷怪蛋</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D45" s="15" t="n">
         <x:v>1</x:v>
@@ -7731,7 +7959,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J45" s="15" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K45" s="15" t="n">
         <x:v>0</x:v>
@@ -7746,7 +7974,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O45" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P45" s="8" t="str">
         <x:v>minecraft:bone</x:v>
@@ -7766,7 +7994,7 @@
         <x:v>猫刷怪蛋</x:v>
       </x:c>
       <x:c r="C46" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D46" s="16" t="n">
         <x:v>1</x:v>
@@ -7787,7 +8015,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J46" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K46" s="16" t="n">
         <x:v>0</x:v>
@@ -7802,7 +8030,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O46" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P46" s="12" t="str">
         <x:v>minecraft:cod</x:v>
@@ -7822,10 +8050,10 @@
         <x:v>蘑菇牛刷怪蛋</x:v>
       </x:c>
       <x:c r="C47" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D47" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E47" s="8" t="str">
         <x:v>红色蘑菇</x:v>
@@ -7843,7 +8071,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J47" s="15" t="n">
-        <x:v>28</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K47" s="15" t="n">
         <x:v>0</x:v>
@@ -7858,7 +8086,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O47" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P47" s="8" t="str">
         <x:v>minecraft:red_mushroom</x:v>
@@ -7878,10 +8106,10 @@
         <x:v>僵尸刷怪蛋</x:v>
       </x:c>
       <x:c r="C48" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D48" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E48" s="12" t="str">
         <x:v>腐肉</x:v>
@@ -7899,7 +8127,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J48" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K48" s="16" t="n">
         <x:v>0</x:v>
@@ -7914,7 +8142,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O48" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P48" s="12" t="str">
         <x:v>minecraft:rotten_flesh</x:v>
@@ -7934,10 +8162,10 @@
         <x:v>骷髅刷怪蛋</x:v>
       </x:c>
       <x:c r="C49" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D49" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E49" s="8" t="str">
         <x:v>骨头</x:v>
@@ -7955,7 +8183,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J49" s="15" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K49" s="15" t="n">
         <x:v>0</x:v>
@@ -7970,7 +8198,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O49" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P49" s="8" t="str">
         <x:v>minecraft:bone</x:v>
@@ -7990,10 +8218,10 @@
         <x:v>蜘蛛刷怪蛋</x:v>
       </x:c>
       <x:c r="C50" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Boughbound Reverie</x:v>
       </x:c>
       <x:c r="D50" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
         <x:v>线</x:v>
@@ -8011,7 +8239,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J50" s="16" t="n">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K50" s="16" t="n">
         <x:v>0</x:v>
@@ -8026,7 +8254,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O50" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:boughbound_reverie</x:v>
       </x:c>
       <x:c r="P50" s="12" t="str">
         <x:v>minecraft:string</x:v>
@@ -8046,10 +8274,10 @@
         <x:v>苦力怕刷怪蛋</x:v>
       </x:c>
       <x:c r="C51" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D51" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E51" s="8" t="str">
         <x:v>火药</x:v>
@@ -8067,7 +8295,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J51" s="15" t="n">
-        <x:v>32</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K51" s="15" t="n">
         <x:v>0</x:v>
@@ -8082,7 +8310,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O51" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P51" s="8" t="str">
         <x:v>minecraft:gunpowder</x:v>
@@ -8102,10 +8330,10 @@
         <x:v>末影人刷怪蛋</x:v>
       </x:c>
       <x:c r="C52" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D52" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
         <x:v>末影珍珠</x:v>
@@ -8123,7 +8351,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J52" s="16" t="n">
-        <x:v>32</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K52" s="16" t="n">
         <x:v>0</x:v>
@@ -8138,7 +8366,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O52" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P52" s="12" t="str">
         <x:v>minecraft:ender_pearl</x:v>
@@ -8158,10 +8386,10 @@
         <x:v>烈焰人刷怪蛋</x:v>
       </x:c>
       <x:c r="C53" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D53" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E53" s="8" t="str">
         <x:v>烈焰棒</x:v>
@@ -8179,7 +8407,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J53" s="15" t="n">
-        <x:v>32</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K53" s="15" t="n">
         <x:v>0</x:v>
@@ -8194,7 +8422,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O53" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P53" s="8" t="str">
         <x:v>minecraft:blaze_rod</x:v>
@@ -8214,10 +8442,10 @@
         <x:v>史莱姆刷怪蛋</x:v>
       </x:c>
       <x:c r="C54" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D54" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
         <x:v>黏液球</x:v>
@@ -8235,7 +8463,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J54" s="16" t="n">
-        <x:v>28</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K54" s="16" t="n">
         <x:v>0</x:v>
@@ -8250,7 +8478,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O54" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P54" s="12" t="str">
         <x:v>minecraft:slime_ball</x:v>
@@ -8270,10 +8498,10 @@
         <x:v>岩浆怪刷怪蛋</x:v>
       </x:c>
       <x:c r="C55" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D55" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E55" s="8" t="str">
         <x:v>岩浆膏</x:v>
@@ -8291,7 +8519,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J55" s="15" t="n">
-        <x:v>32</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K55" s="15" t="n">
         <x:v>0</x:v>
@@ -8306,7 +8534,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O55" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P55" s="8" t="str">
         <x:v>minecraft:magma_cream</x:v>
@@ -8326,10 +8554,10 @@
         <x:v>守卫者刷怪蛋</x:v>
       </x:c>
       <x:c r="C56" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>Stillwater Palimpsest</x:v>
       </x:c>
       <x:c r="D56" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
         <x:v>海晶碎片</x:v>
@@ -8347,7 +8575,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J56" s="16" t="n">
-        <x:v>36</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K56" s="16" t="n">
         <x:v>0</x:v>
@@ -8362,7 +8590,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O56" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:stillwater_palimpsest</x:v>
       </x:c>
       <x:c r="P56" s="12" t="str">
         <x:v>minecraft:prismarine_shard</x:v>
@@ -8382,10 +8610,10 @@
         <x:v>潜影贝刷怪蛋</x:v>
       </x:c>
       <x:c r="C57" s="8" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D57" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E57" s="8" t="str">
         <x:v>潜影壳</x:v>
@@ -8403,7 +8631,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J57" s="15" t="n">
-        <x:v>48</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K57" s="15" t="n">
         <x:v>0</x:v>
@@ -8418,7 +8646,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O57" s="8" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P57" s="8" t="str">
         <x:v>minecraft:shulker_shell</x:v>
@@ -8438,10 +8666,10 @@
         <x:v>硫磺史莱姆刷怪蛋</x:v>
       </x:c>
       <x:c r="C58" s="12" t="str">
-        <x:v>鸡蛋</x:v>
+        <x:v>The Unwrought Facet</x:v>
       </x:c>
       <x:c r="D58" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
         <x:v>硫黄</x:v>
@@ -8459,7 +8687,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J58" s="16" t="n">
-        <x:v>36</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K58" s="16" t="n">
         <x:v>0</x:v>
@@ -8474,7 +8702,7 @@
         <x:v>启用</x:v>
       </x:c>
       <x:c r="O58" s="12" t="str">
-        <x:v>minecraft:egg</x:v>
+        <x:v>convert_table:unwrought_facet</x:v>
       </x:c>
       <x:c r="P58" s="12" t="str">
         <x:v>minecraft:sulfur</x:v>
@@ -8515,7 +8743,7 @@
         <x:v>卷心菜种子、番茄种子、稻米、洋葱</x:v>
       </x:c>
       <x:c r="J59" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K59" s="15" t="n">
         <x:v>0</x:v>
@@ -8571,7 +8799,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J60" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K60" s="16" t="n">
         <x:v>0</x:v>
@@ -8625,7 +8853,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J61" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K61" s="15" t="n">
         <x:v>0</x:v>
@@ -8679,7 +8907,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J62" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K62" s="16" t="n">
         <x:v>0</x:v>
@@ -8733,7 +8961,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J63" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K63" s="15" t="n">
         <x:v>0</x:v>
@@ -8787,7 +9015,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J64" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K64" s="16" t="n">
         <x:v>0</x:v>
@@ -8841,7 +9069,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J65" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K65" s="15" t="n">
         <x:v>0</x:v>
@@ -8895,7 +9123,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J66" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K66" s="16" t="n">
         <x:v>0</x:v>
@@ -8949,7 +9177,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J67" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K67" s="15" t="n">
         <x:v>0</x:v>
@@ -9003,7 +9231,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J68" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K68" s="16" t="n">
         <x:v>0</x:v>
@@ -9057,7 +9285,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J69" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K69" s="15" t="n">
         <x:v>0</x:v>
@@ -9111,7 +9339,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J70" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K70" s="16" t="n">
         <x:v>0</x:v>
@@ -9165,7 +9393,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J71" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K71" s="15" t="n">
         <x:v>0</x:v>
@@ -9219,7 +9447,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J72" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K72" s="16" t="n">
         <x:v>0</x:v>
@@ -9273,7 +9501,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J73" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K73" s="15" t="n">
         <x:v>0</x:v>
@@ -9327,7 +9555,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J74" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K74" s="16" t="n">
         <x:v>0</x:v>
@@ -9381,7 +9609,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J75" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K75" s="15" t="n">
         <x:v>0</x:v>
@@ -9435,7 +9663,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J76" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K76" s="16" t="n">
         <x:v>0</x:v>
@@ -9489,7 +9717,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J77" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K77" s="15" t="n">
         <x:v>0</x:v>
@@ -9543,7 +9771,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J78" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K78" s="16" t="n">
         <x:v>0</x:v>
@@ -9597,7 +9825,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J79" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K79" s="15" t="n">
         <x:v>0</x:v>
@@ -9651,7 +9879,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J80" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K80" s="16" t="n">
         <x:v>0</x:v>
@@ -9705,7 +9933,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J81" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K81" s="15" t="n">
         <x:v>0</x:v>
@@ -9759,7 +9987,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J82" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K82" s="16" t="n">
         <x:v>0</x:v>
@@ -9813,7 +10041,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J83" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K83" s="15" t="n">
         <x:v>0</x:v>
@@ -9867,7 +10095,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J84" s="16" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K84" s="16" t="n">
         <x:v>0</x:v>
@@ -9921,7 +10149,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J85" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K85" s="15" t="n">
         <x:v>0</x:v>
@@ -9975,7 +10203,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J86" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K86" s="16" t="n">
         <x:v>0</x:v>
@@ -10031,7 +10259,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J87" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K87" s="15" t="n">
         <x:v>0</x:v>
@@ -10087,7 +10315,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J88" s="16" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K88" s="16" t="n">
         <x:v>0</x:v>
@@ -10143,7 +10371,7 @@
         <x:v>无（定向）</x:v>
       </x:c>
       <x:c r="J89" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K89" s="15" t="n">
         <x:v>0</x:v>
@@ -10167,13 +10395,1973 @@
         <x:v>minecraft:pufferfish_bucket</x:v>
       </x:c>
       <x:c r="R89" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="48" customHeight="1">
+      <x:c r="A90" s="12" t="str">
+        <x:v>form-allay</x:v>
+      </x:c>
+      <x:c r="B90" s="12" t="str">
+        <x:v>悦灵塑形</x:v>
+      </x:c>
+      <x:c r="C90" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D90" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E90" s="12" t="str">
+        <x:v>紫水晶碎片</x:v>
+      </x:c>
+      <x:c r="F90" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G90" s="12" t="str">
+        <x:v>悦灵刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H90" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I90" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J90" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K90" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M90" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N90" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O90" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P90" s="12" t="str">
+        <x:v>minecraft:amethyst_shard</x:v>
+      </x:c>
+      <x:c r="Q90" s="12" t="str">
+        <x:v>minecraft:allay_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R90" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="48" customHeight="1">
+      <x:c r="A91" s="8" t="str">
+        <x:v>form-armadillo</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="str">
+        <x:v>犰狳塑形</x:v>
+      </x:c>
+      <x:c r="C91" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D91" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E91" s="8" t="str">
+        <x:v>蜘蛛眼</x:v>
+      </x:c>
+      <x:c r="F91" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G91" s="8" t="str">
+        <x:v>犰狳刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H91" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I91" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J91" s="15" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K91" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M91" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N91" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O91" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P91" s="8" t="str">
+        <x:v>minecraft:spider_eye</x:v>
+      </x:c>
+      <x:c r="Q91" s="8" t="str">
+        <x:v>minecraft:armadillo_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R91" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="48" customHeight="1">
+      <x:c r="A92" s="12" t="str">
+        <x:v>form-axolotl</x:v>
+      </x:c>
+      <x:c r="B92" s="12" t="str">
+        <x:v>美西螈塑形</x:v>
+      </x:c>
+      <x:c r="C92" s="12" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D92" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E92" s="12" t="str">
+        <x:v>黏土球</x:v>
+      </x:c>
+      <x:c r="F92" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G92" s="12" t="str">
+        <x:v>美西螈刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H92" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I92" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J92" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K92" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L92" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M92" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N92" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O92" s="12" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P92" s="12" t="str">
+        <x:v>minecraft:clay_ball</x:v>
+      </x:c>
+      <x:c r="Q92" s="12" t="str">
+        <x:v>minecraft:axolotl_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R92" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="48" customHeight="1">
+      <x:c r="A93" s="8" t="str">
+        <x:v>form-bat</x:v>
+      </x:c>
+      <x:c r="B93" s="8" t="str">
+        <x:v>蝙蝠塑形</x:v>
+      </x:c>
+      <x:c r="C93" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D93" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E93" s="8" t="str">
+        <x:v>棕色蘑菇</x:v>
+      </x:c>
+      <x:c r="F93" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G93" s="8" t="str">
+        <x:v>蝙蝠刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H93" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I93" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J93" s="15" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K93" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L93" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M93" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N93" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O93" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P93" s="8" t="str">
+        <x:v>minecraft:brown_mushroom</x:v>
+      </x:c>
+      <x:c r="Q93" s="8" t="str">
+        <x:v>minecraft:bat_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R93" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="48" customHeight="1">
+      <x:c r="A94" s="12" t="str">
+        <x:v>form-cod</x:v>
+      </x:c>
+      <x:c r="B94" s="12" t="str">
+        <x:v>鳕鱼塑形</x:v>
+      </x:c>
+      <x:c r="C94" s="12" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D94" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E94" s="12" t="str">
+        <x:v>海草</x:v>
+      </x:c>
+      <x:c r="F94" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G94" s="12" t="str">
+        <x:v>鳕鱼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H94" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I94" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J94" s="16" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K94" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L94" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M94" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N94" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O94" s="12" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P94" s="12" t="str">
+        <x:v>minecraft:seagrass</x:v>
+      </x:c>
+      <x:c r="Q94" s="12" t="str">
+        <x:v>minecraft:cod_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R94" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="48" customHeight="1">
+      <x:c r="A95" s="8" t="str">
+        <x:v>form-salmon</x:v>
+      </x:c>
+      <x:c r="B95" s="8" t="str">
+        <x:v>鲑鱼塑形</x:v>
+      </x:c>
+      <x:c r="C95" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D95" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E95" s="8" t="str">
+        <x:v>海草</x:v>
+      </x:c>
+      <x:c r="F95" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G95" s="8" t="str">
+        <x:v>鲑鱼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H95" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I95" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J95" s="15" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K95" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M95" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N95" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O95" s="8" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P95" s="8" t="str">
+        <x:v>minecraft:seagrass</x:v>
+      </x:c>
+      <x:c r="Q95" s="8" t="str">
+        <x:v>minecraft:salmon_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R95" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="48" customHeight="1">
+      <x:c r="A96" s="12" t="str">
+        <x:v>form-tropical-fish</x:v>
+      </x:c>
+      <x:c r="B96" s="12" t="str">
+        <x:v>热带鱼塑形</x:v>
+      </x:c>
+      <x:c r="C96" s="12" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D96" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E96" s="12" t="str">
+        <x:v>海草</x:v>
+      </x:c>
+      <x:c r="F96" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G96" s="12" t="str">
+        <x:v>热带鱼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H96" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I96" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J96" s="16" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K96" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L96" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M96" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N96" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O96" s="12" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P96" s="12" t="str">
+        <x:v>minecraft:seagrass</x:v>
+      </x:c>
+      <x:c r="Q96" s="12" t="str">
+        <x:v>minecraft:tropical_fish_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R96" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="48" customHeight="1">
+      <x:c r="A97" s="8" t="str">
+        <x:v>form-pufferfish</x:v>
+      </x:c>
+      <x:c r="B97" s="8" t="str">
+        <x:v>河豚塑形</x:v>
+      </x:c>
+      <x:c r="C97" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D97" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E97" s="8" t="str">
+        <x:v>海带</x:v>
+      </x:c>
+      <x:c r="F97" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G97" s="8" t="str">
+        <x:v>河豚刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H97" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I97" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J97" s="15" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K97" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L97" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M97" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N97" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O97" s="8" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P97" s="8" t="str">
+        <x:v>minecraft:kelp</x:v>
+      </x:c>
+      <x:c r="Q97" s="8" t="str">
+        <x:v>minecraft:pufferfish_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R97" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="48" customHeight="1">
+      <x:c r="A98" s="12" t="str">
+        <x:v>form-copper-golem</x:v>
+      </x:c>
+      <x:c r="B98" s="12" t="str">
+        <x:v>铜傀儡塑形</x:v>
+      </x:c>
+      <x:c r="C98" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D98" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E98" s="12" t="str">
+        <x:v>红石粉</x:v>
+      </x:c>
+      <x:c r="F98" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G98" s="12" t="str">
+        <x:v>铜傀儡刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H98" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I98" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J98" s="16" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="K98" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M98" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N98" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O98" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P98" s="12" t="str">
+        <x:v>minecraft:redstone</x:v>
+      </x:c>
+      <x:c r="Q98" s="12" t="str">
+        <x:v>minecraft:copper_golem_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R98" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="48" customHeight="1">
+      <x:c r="A99" s="8" t="str">
+        <x:v>form-dolphin</x:v>
+      </x:c>
+      <x:c r="B99" s="8" t="str">
+        <x:v>海豚塑形</x:v>
+      </x:c>
+      <x:c r="C99" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D99" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E99" s="8" t="str">
+        <x:v>海带</x:v>
+      </x:c>
+      <x:c r="F99" s="15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G99" s="8" t="str">
+        <x:v>海豚刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H99" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I99" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J99" s="15" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K99" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L99" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M99" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N99" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O99" s="8" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P99" s="8" t="str">
+        <x:v>minecraft:kelp</x:v>
+      </x:c>
+      <x:c r="Q99" s="8" t="str">
+        <x:v>minecraft:dolphin_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R99" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="48" customHeight="1">
+      <x:c r="A100" s="12" t="str">
+        <x:v>form-donkey</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="str">
+        <x:v>驴塑形</x:v>
+      </x:c>
+      <x:c r="C100" s="12" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D100" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E100" s="12" t="str">
+        <x:v>干草捆</x:v>
+      </x:c>
+      <x:c r="F100" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G100" s="12" t="str">
+        <x:v>驴刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H100" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I100" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J100" s="16" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K100" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L100" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M100" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N100" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O100" s="12" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P100" s="12" t="str">
+        <x:v>minecraft:hay_block</x:v>
+      </x:c>
+      <x:c r="Q100" s="12" t="str">
+        <x:v>minecraft:donkey_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R100" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="48" customHeight="1">
+      <x:c r="A101" s="8" t="str">
+        <x:v>form-fox</x:v>
+      </x:c>
+      <x:c r="B101" s="8" t="str">
+        <x:v>狐狸塑形</x:v>
+      </x:c>
+      <x:c r="C101" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D101" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E101" s="8" t="str">
+        <x:v>甜浆果</x:v>
+      </x:c>
+      <x:c r="F101" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G101" s="8" t="str">
+        <x:v>狐狸刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H101" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I101" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J101" s="15" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K101" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M101" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N101" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O101" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P101" s="8" t="str">
+        <x:v>minecraft:sweet_berries</x:v>
+      </x:c>
+      <x:c r="Q101" s="8" t="str">
+        <x:v>minecraft:fox_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R101" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="48" customHeight="1">
+      <x:c r="A102" s="12" t="str">
+        <x:v>form-happy-ghast</x:v>
+      </x:c>
+      <x:c r="B102" s="12" t="str">
+        <x:v>快乐恶魂塑形</x:v>
+      </x:c>
+      <x:c r="C102" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D102" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E102" s="12" t="str">
+        <x:v>雪块</x:v>
+      </x:c>
+      <x:c r="F102" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G102" s="12" t="str">
+        <x:v>快乐恶魂刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H102" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I102" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J102" s="16" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="K102" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L102" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M102" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N102" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O102" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P102" s="12" t="str">
+        <x:v>minecraft:snow_block</x:v>
+      </x:c>
+      <x:c r="Q102" s="12" t="str">
+        <x:v>minecraft:happy_ghast_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R102" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="48" customHeight="1">
+      <x:c r="A103" s="8" t="str">
+        <x:v>form-horse</x:v>
+      </x:c>
+      <x:c r="B103" s="8" t="str">
+        <x:v>马塑形</x:v>
+      </x:c>
+      <x:c r="C103" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D103" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E103" s="8" t="str">
+        <x:v>干草捆</x:v>
+      </x:c>
+      <x:c r="F103" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G103" s="8" t="str">
+        <x:v>马刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H103" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I103" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J103" s="15" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K103" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L103" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M103" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N103" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O103" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P103" s="8" t="str">
+        <x:v>minecraft:hay_block</x:v>
+      </x:c>
+      <x:c r="Q103" s="8" t="str">
+        <x:v>minecraft:horse_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R103" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="48" customHeight="1">
+      <x:c r="A104" s="12" t="str">
+        <x:v>form-iron-golem</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="str">
+        <x:v>铁傀儡塑形</x:v>
+      </x:c>
+      <x:c r="C104" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D104" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E104" s="12" t="str">
+        <x:v>红石粉</x:v>
+      </x:c>
+      <x:c r="F104" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G104" s="12" t="str">
+        <x:v>铁傀儡刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H104" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I104" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J104" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K104" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L104" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M104" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N104" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O104" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P104" s="12" t="str">
+        <x:v>minecraft:redstone</x:v>
+      </x:c>
+      <x:c r="Q104" s="12" t="str">
+        <x:v>minecraft:iron_golem_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R104" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="48" customHeight="1">
+      <x:c r="A105" s="8" t="str">
+        <x:v>form-llama</x:v>
+      </x:c>
+      <x:c r="B105" s="8" t="str">
+        <x:v>羊驼塑形</x:v>
+      </x:c>
+      <x:c r="C105" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D105" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E105" s="8" t="str">
+        <x:v>干草捆</x:v>
+      </x:c>
+      <x:c r="F105" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G105" s="8" t="str">
+        <x:v>羊驼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H105" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I105" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J105" s="15" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K105" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M105" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N105" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O105" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P105" s="8" t="str">
+        <x:v>minecraft:hay_block</x:v>
+      </x:c>
+      <x:c r="Q105" s="8" t="str">
+        <x:v>minecraft:llama_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R105" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="48" customHeight="1">
+      <x:c r="A106" s="12" t="str">
+        <x:v>form-mule</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="str">
+        <x:v>骡塑形</x:v>
+      </x:c>
+      <x:c r="C106" s="12" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D106" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E106" s="12" t="str">
+        <x:v>干草捆</x:v>
+      </x:c>
+      <x:c r="F106" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G106" s="12" t="str">
+        <x:v>骡刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H106" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I106" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J106" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K106" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M106" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N106" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O106" s="12" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P106" s="12" t="str">
+        <x:v>minecraft:hay_block</x:v>
+      </x:c>
+      <x:c r="Q106" s="12" t="str">
+        <x:v>minecraft:mule_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R106" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="48" customHeight="1">
+      <x:c r="A107" s="8" t="str">
+        <x:v>form-nautilus</x:v>
+      </x:c>
+      <x:c r="B107" s="8" t="str">
+        <x:v>鹦鹉螺塑形</x:v>
+      </x:c>
+      <x:c r="C107" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D107" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E107" s="8" t="str">
+        <x:v>海带</x:v>
+      </x:c>
+      <x:c r="F107" s="15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G107" s="8" t="str">
+        <x:v>鹦鹉螺刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H107" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I107" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J107" s="15" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K107" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L107" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M107" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N107" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O107" s="8" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P107" s="8" t="str">
+        <x:v>minecraft:kelp</x:v>
+      </x:c>
+      <x:c r="Q107" s="8" t="str">
+        <x:v>minecraft:nautilus_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R107" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="48" customHeight="1">
+      <x:c r="A108" s="12" t="str">
+        <x:v>form-ocelot</x:v>
+      </x:c>
+      <x:c r="B108" s="12" t="str">
+        <x:v>豹猫塑形</x:v>
+      </x:c>
+      <x:c r="C108" s="12" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D108" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E108" s="12" t="str">
+        <x:v>生鲑鱼</x:v>
+      </x:c>
+      <x:c r="F108" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G108" s="12" t="str">
+        <x:v>豹猫刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H108" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I108" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J108" s="16" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K108" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M108" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N108" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O108" s="12" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P108" s="12" t="str">
+        <x:v>minecraft:salmon</x:v>
+      </x:c>
+      <x:c r="Q108" s="12" t="str">
+        <x:v>minecraft:ocelot_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R108" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="48" customHeight="1">
+      <x:c r="A109" s="8" t="str">
+        <x:v>form-panda</x:v>
+      </x:c>
+      <x:c r="B109" s="8" t="str">
+        <x:v>熊猫塑形</x:v>
+      </x:c>
+      <x:c r="C109" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D109" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E109" s="8" t="str">
+        <x:v>竹子</x:v>
+      </x:c>
+      <x:c r="F109" s="15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>熊猫刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H109" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I109" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J109" s="15" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K109" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M109" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N109" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O109" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P109" s="8" t="str">
+        <x:v>minecraft:bamboo</x:v>
+      </x:c>
+      <x:c r="Q109" s="8" t="str">
+        <x:v>minecraft:panda_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R109" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="48" customHeight="1">
+      <x:c r="A110" s="12" t="str">
+        <x:v>form-parrot</x:v>
+      </x:c>
+      <x:c r="B110" s="12" t="str">
+        <x:v>鹦鹉塑形</x:v>
+      </x:c>
+      <x:c r="C110" s="12" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D110" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E110" s="12" t="str">
+        <x:v>小麦种子</x:v>
+      </x:c>
+      <x:c r="F110" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G110" s="12" t="str">
+        <x:v>鹦鹉刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H110" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I110" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J110" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K110" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M110" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N110" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O110" s="12" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P110" s="12" t="str">
+        <x:v>minecraft:wheat_seeds</x:v>
+      </x:c>
+      <x:c r="Q110" s="12" t="str">
+        <x:v>minecraft:parrot_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R110" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="48" customHeight="1">
+      <x:c r="A111" s="8" t="str">
+        <x:v>form-polar-bear</x:v>
+      </x:c>
+      <x:c r="B111" s="8" t="str">
+        <x:v>北极熊塑形</x:v>
+      </x:c>
+      <x:c r="C111" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D111" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E111" s="8" t="str">
+        <x:v>雪块</x:v>
+      </x:c>
+      <x:c r="F111" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>北极熊刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H111" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I111" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J111" s="15" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K111" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L111" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M111" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N111" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O111" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P111" s="8" t="str">
+        <x:v>minecraft:snow_block</x:v>
+      </x:c>
+      <x:c r="Q111" s="8" t="str">
+        <x:v>minecraft:polar_bear_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R111" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="48" customHeight="1">
+      <x:c r="A112" s="12" t="str">
+        <x:v>form-skeleton-horse</x:v>
+      </x:c>
+      <x:c r="B112" s="12" t="str">
+        <x:v>骷髅马塑形</x:v>
+      </x:c>
+      <x:c r="C112" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D112" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E112" s="12" t="str">
+        <x:v>苔藓块</x:v>
+      </x:c>
+      <x:c r="F112" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G112" s="12" t="str">
+        <x:v>骷髅马刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H112" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I112" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J112" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K112" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L112" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M112" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N112" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O112" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P112" s="12" t="str">
+        <x:v>minecraft:moss_block</x:v>
+      </x:c>
+      <x:c r="Q112" s="12" t="str">
+        <x:v>minecraft:skeleton_horse_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R112" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="48" customHeight="1">
+      <x:c r="A113" s="8" t="str">
+        <x:v>form-sniffer</x:v>
+      </x:c>
+      <x:c r="B113" s="8" t="str">
+        <x:v>嗅探兽塑形</x:v>
+      </x:c>
+      <x:c r="C113" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D113" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E113" s="8" t="str">
+        <x:v>苔藓块</x:v>
+      </x:c>
+      <x:c r="F113" s="15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G113" s="8" t="str">
+        <x:v>嗅探兽刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H113" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I113" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J113" s="15" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K113" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L113" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M113" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N113" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O113" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P113" s="8" t="str">
+        <x:v>minecraft:moss_block</x:v>
+      </x:c>
+      <x:c r="Q113" s="8" t="str">
+        <x:v>minecraft:sniffer_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R113" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="48" customHeight="1">
+      <x:c r="A114" s="12" t="str">
+        <x:v>form-snow-golem</x:v>
+      </x:c>
+      <x:c r="B114" s="12" t="str">
+        <x:v>雪傀儡塑形</x:v>
+      </x:c>
+      <x:c r="C114" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D114" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E114" s="12" t="str">
+        <x:v>雕刻南瓜</x:v>
+      </x:c>
+      <x:c r="F114" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="12" t="str">
+        <x:v>雪傀儡刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H114" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I114" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J114" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K114" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M114" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N114" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O114" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P114" s="12" t="str">
+        <x:v>minecraft:carved_pumpkin</x:v>
+      </x:c>
+      <x:c r="Q114" s="12" t="str">
+        <x:v>minecraft:snow_golem_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R114" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="48" customHeight="1">
+      <x:c r="A115" s="8" t="str">
+        <x:v>form-squid</x:v>
+      </x:c>
+      <x:c r="B115" s="8" t="str">
+        <x:v>鱿鱼塑形</x:v>
+      </x:c>
+      <x:c r="C115" s="8" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D115" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E115" s="8" t="str">
+        <x:v>海带</x:v>
+      </x:c>
+      <x:c r="F115" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G115" s="8" t="str">
+        <x:v>鱿鱼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H115" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I115" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J115" s="15" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K115" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M115" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N115" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O115" s="8" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P115" s="8" t="str">
+        <x:v>minecraft:kelp</x:v>
+      </x:c>
+      <x:c r="Q115" s="8" t="str">
+        <x:v>minecraft:squid_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R115" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="48" customHeight="1">
+      <x:c r="A116" s="12" t="str">
+        <x:v>form-glow-squid</x:v>
+      </x:c>
+      <x:c r="B116" s="12" t="str">
+        <x:v>发光鱿鱼塑形</x:v>
+      </x:c>
+      <x:c r="C116" s="12" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D116" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E116" s="12" t="str">
+        <x:v>发光地衣</x:v>
+      </x:c>
+      <x:c r="F116" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G116" s="12" t="str">
+        <x:v>发光鱿鱼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H116" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I116" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J116" s="16" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K116" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M116" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N116" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O116" s="12" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P116" s="12" t="str">
+        <x:v>minecraft:glow_lichen</x:v>
+      </x:c>
+      <x:c r="Q116" s="12" t="str">
+        <x:v>minecraft:glow_squid_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R116" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="48" customHeight="1">
+      <x:c r="A117" s="8" t="str">
+        <x:v>form-strider</x:v>
+      </x:c>
+      <x:c r="B117" s="8" t="str">
+        <x:v>炽足兽塑形</x:v>
+      </x:c>
+      <x:c r="C117" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D117" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E117" s="8" t="str">
+        <x:v>诡异菌</x:v>
+      </x:c>
+      <x:c r="F117" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G117" s="8" t="str">
+        <x:v>炽足兽刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H117" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I117" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J117" s="15" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K117" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L117" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M117" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N117" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O117" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P117" s="8" t="str">
+        <x:v>minecraft:warped_fungus</x:v>
+      </x:c>
+      <x:c r="Q117" s="8" t="str">
+        <x:v>minecraft:strider_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R117" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="48" customHeight="1">
+      <x:c r="A118" s="12" t="str">
+        <x:v>form-tadpole</x:v>
+      </x:c>
+      <x:c r="B118" s="12" t="str">
+        <x:v>蝌蚪塑形</x:v>
+      </x:c>
+      <x:c r="C118" s="12" t="str">
+        <x:v>Stillwater Palimpsest</x:v>
+      </x:c>
+      <x:c r="D118" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E118" s="12" t="str">
+        <x:v>黏液球</x:v>
+      </x:c>
+      <x:c r="F118" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G118" s="12" t="str">
+        <x:v>蝌蚪刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H118" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I118" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J118" s="16" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K118" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L118" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M118" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N118" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O118" s="12" t="str">
+        <x:v>convert_table:stillwater_palimpsest</x:v>
+      </x:c>
+      <x:c r="P118" s="12" t="str">
+        <x:v>minecraft:slime_ball</x:v>
+      </x:c>
+      <x:c r="Q118" s="12" t="str">
+        <x:v>minecraft:tadpole_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R118" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="48" customHeight="1">
+      <x:c r="A119" s="8" t="str">
+        <x:v>form-trader-llama</x:v>
+      </x:c>
+      <x:c r="B119" s="8" t="str">
+        <x:v>行商羊驼塑形</x:v>
+      </x:c>
+      <x:c r="C119" s="8" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="D119" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E119" s="8" t="str">
+        <x:v>干草捆</x:v>
+      </x:c>
+      <x:c r="F119" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G119" s="8" t="str">
+        <x:v>行商羊驼刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H119" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I119" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J119" s="15" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K119" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L119" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M119" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N119" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O119" s="8" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="P119" s="8" t="str">
+        <x:v>minecraft:hay_block</x:v>
+      </x:c>
+      <x:c r="Q119" s="8" t="str">
+        <x:v>minecraft:trader_llama_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R119" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="48" customHeight="1">
+      <x:c r="A120" s="12" t="str">
+        <x:v>form-villager</x:v>
+      </x:c>
+      <x:c r="B120" s="12" t="str">
+        <x:v>村民塑形</x:v>
+      </x:c>
+      <x:c r="C120" s="12" t="str">
+        <x:v>Unbroken Cognizance</x:v>
+      </x:c>
+      <x:c r="D120" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E120" s="12" t="str">
+        <x:v>小麦</x:v>
+      </x:c>
+      <x:c r="F120" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G120" s="12" t="str">
+        <x:v>村民刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H120" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I120" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J120" s="16" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K120" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M120" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N120" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O120" s="12" t="str">
+        <x:v>convert_table:unbroken_cognizance</x:v>
+      </x:c>
+      <x:c r="P120" s="12" t="str">
+        <x:v>minecraft:wheat</x:v>
+      </x:c>
+      <x:c r="Q120" s="12" t="str">
+        <x:v>minecraft:villager_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R120" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="48" customHeight="1">
+      <x:c r="A121" s="8" t="str">
+        <x:v>form-wandering-trader</x:v>
+      </x:c>
+      <x:c r="B121" s="8" t="str">
+        <x:v>流浪商人塑形</x:v>
+      </x:c>
+      <x:c r="C121" s="8" t="str">
+        <x:v>Unbroken Cognizance</x:v>
+      </x:c>
+      <x:c r="D121" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E121" s="8" t="str">
+        <x:v>西瓜片</x:v>
+      </x:c>
+      <x:c r="F121" s="15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G121" s="8" t="str">
+        <x:v>流浪商人刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H121" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I121" s="8" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J121" s="15" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K121" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M121" s="8" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N121" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O121" s="8" t="str">
+        <x:v>convert_table:unbroken_cognizance</x:v>
+      </x:c>
+      <x:c r="P121" s="8" t="str">
+        <x:v>minecraft:melon_slice</x:v>
+      </x:c>
+      <x:c r="Q121" s="8" t="str">
+        <x:v>minecraft:wandering_trader_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R121" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="48" customHeight="1">
+      <x:c r="A122" s="12" t="str">
+        <x:v>form-zombie-horse</x:v>
+      </x:c>
+      <x:c r="B122" s="12" t="str">
+        <x:v>僵尸马塑形</x:v>
+      </x:c>
+      <x:c r="C122" s="12" t="str">
+        <x:v>The Unwrought Facet</x:v>
+      </x:c>
+      <x:c r="D122" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E122" s="12" t="str">
+        <x:v>棕色蘑菇</x:v>
+      </x:c>
+      <x:c r="F122" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G122" s="12" t="str">
+        <x:v>僵尸马刷怪蛋</x:v>
+      </x:c>
+      <x:c r="H122" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I122" s="12" t="str">
+        <x:v>无（定向）</x:v>
+      </x:c>
+      <x:c r="J122" s="16" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K122" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M122" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N122" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O122" s="12" t="str">
+        <x:v>convert_table:unwrought_facet</x:v>
+      </x:c>
+      <x:c r="P122" s="12" t="str">
+        <x:v>minecraft:brown_mushroom</x:v>
+      </x:c>
+      <x:c r="Q122" s="12" t="str">
+        <x:v>minecraft:zombie_horse_spawn_egg</x:v>
+      </x:c>
+      <x:c r="R122" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="48" customHeight="1">
+      <x:c r="A123" s="8" t="str">
+        <x:v>seed-vanilla-crops</x:v>
+      </x:c>
+      <x:c r="B123" s="8" t="str">
+        <x:v>原版作物种子抽卡</x:v>
+      </x:c>
+      <x:c r="C123" s="8" t="str">
+        <x:v>小麦种子</x:v>
+      </x:c>
+      <x:c r="D123" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E123" s="8" t="str">
+        <x:v>骨粉</x:v>
+      </x:c>
+      <x:c r="F123" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G123" s="8" t="str">
+        <x:v>南瓜种子</x:v>
+      </x:c>
+      <x:c r="H123" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I123" s="8" t="str">
+        <x:v>小麦种子、南瓜种子、西瓜种子、甜菜种子、胡萝卜、马铃薯</x:v>
+      </x:c>
+      <x:c r="J123" s="15" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K123" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L123" s="8" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M123" s="8" t="str">
+        <x:v>允许连续/容器</x:v>
+      </x:c>
+      <x:c r="N123" s="8" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O123" s="8" t="str">
+        <x:v>minecraft:wheat_seeds</x:v>
+      </x:c>
+      <x:c r="P123" s="8" t="str">
+        <x:v>minecraft:bone_meal</x:v>
+      </x:c>
+      <x:c r="Q123" s="8" t="str">
+        <x:v>minecraft:pumpkin_seeds</x:v>
+      </x:c>
+      <x:c r="R123" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="48" customHeight="1">
+      <x:c r="A124" s="12" t="str">
+        <x:v>seed-ancient-crops</x:v>
+      </x:c>
+      <x:c r="B124" s="12" t="str">
+        <x:v>远古作物种子抽卡</x:v>
+      </x:c>
+      <x:c r="C124" s="12" t="str">
+        <x:v>小麦种子</x:v>
+      </x:c>
+      <x:c r="D124" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E124" s="12" t="str">
+        <x:v>Boughbound Reverie</x:v>
+      </x:c>
+      <x:c r="F124" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" s="12" t="str">
+        <x:v>火把花种子</x:v>
+      </x:c>
+      <x:c r="H124" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I124" s="12" t="str">
+        <x:v>火把花种子、瓶子草荚果</x:v>
+      </x:c>
+      <x:c r="J124" s="16" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K124" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" s="12" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="M124" s="12" t="str">
+        <x:v>仅投入槽手动</x:v>
+      </x:c>
+      <x:c r="N124" s="12" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="O124" s="12" t="str">
+        <x:v>minecraft:wheat_seeds</x:v>
+      </x:c>
+      <x:c r="P124" s="12" t="str">
+        <x:v>convert_table:boughbound_reverie</x:v>
+      </x:c>
+      <x:c r="Q124" s="12" t="str">
+        <x:v>minecraft:torchflower_seeds</x:v>
+      </x:c>
+      <x:c r="R124" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ecf549ee3b4681"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re20cd67569ea4397"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10192,6 +12380,9 @@
     <x:col min="5" max="5" width="63" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="46" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
@@ -10217,7 +12408,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>木材用对应树苗或菌类；其他原料用紫水晶碎片、回响碎片等自然或魔法触媒。每次产出 1 件；触媒不消耗。放入触媒、选定产物后开启增殖；界面显示产速与下一件进度，产速 = 当前分配的生长因子/秒 ÷ 单件成本。</x:v>
+        <x:v>放入触媒和一件目标物品作源本，两者都不消耗；每次产出 1 件。小/中/大/成熟晶芽自然内涵量为 16/64、8/64、4/64、1/64；未成熟晶芽每秒抽取上限 1/64，方解石为 2/64。产速 = 分配的生长因子/秒 ÷ 单件成本。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10247,6 +12438,15 @@
       <x:c r="G6" s="26" t="str">
         <x:v>产物 ID</x:v>
       </x:c>
+      <x:c r="H6" s="26" t="str">
+        <x:v>源本（不消耗）</x:v>
+      </x:c>
+      <x:c r="I6" s="26" t="str">
+        <x:v>源本数量</x:v>
+      </x:c>
+      <x:c r="J6" s="26" t="str">
+        <x:v>源本 ID</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="8" t="str">
@@ -10270,6 +12470,15 @@
       <x:c r="G7" s="8" t="str">
         <x:v>minecraft:oak_log</x:v>
       </x:c>
+      <x:c r="H7" s="8" t="str">
+        <x:v>橡木原木</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="8" t="str">
+        <x:v>minecraft:oak_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="12" t="str">
@@ -10293,6 +12502,15 @@
       <x:c r="G8" s="12" t="str">
         <x:v>minecraft:spruce_log</x:v>
       </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>云杉原木</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="12" t="str">
+        <x:v>minecraft:spruce_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="8" t="str">
@@ -10316,6 +12534,15 @@
       <x:c r="G9" s="8" t="str">
         <x:v>minecraft:birch_log</x:v>
       </x:c>
+      <x:c r="H9" s="8" t="str">
+        <x:v>白桦原木</x:v>
+      </x:c>
+      <x:c r="I9" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="8" t="str">
+        <x:v>minecraft:birch_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="12" t="str">
@@ -10339,6 +12566,15 @@
       <x:c r="G10" s="12" t="str">
         <x:v>minecraft:jungle_log</x:v>
       </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>丛林原木</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="str">
+        <x:v>minecraft:jungle_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
       <x:c r="A11" s="8" t="str">
@@ -10362,6 +12598,15 @@
       <x:c r="G11" s="8" t="str">
         <x:v>minecraft:acacia_log</x:v>
       </x:c>
+      <x:c r="H11" s="8" t="str">
+        <x:v>金合欢原木</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="8" t="str">
+        <x:v>minecraft:acacia_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
       <x:c r="A12" s="12" t="str">
@@ -10385,6 +12630,15 @@
       <x:c r="G12" s="12" t="str">
         <x:v>minecraft:dark_oak_log</x:v>
       </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>深色橡木原木</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="str">
+        <x:v>minecraft:dark_oak_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
       <x:c r="A13" s="8" t="str">
@@ -10408,6 +12662,15 @@
       <x:c r="G13" s="8" t="str">
         <x:v>minecraft:cherry_log</x:v>
       </x:c>
+      <x:c r="H13" s="8" t="str">
+        <x:v>樱花原木</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="8" t="str">
+        <x:v>minecraft:cherry_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
       <x:c r="A14" s="12" t="str">
@@ -10431,6 +12694,15 @@
       <x:c r="G14" s="12" t="str">
         <x:v>minecraft:pale_oak_log</x:v>
       </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>苍白橡木原木</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="str">
+        <x:v>minecraft:pale_oak_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
       <x:c r="A15" s="8" t="str">
@@ -10454,6 +12726,15 @@
       <x:c r="G15" s="8" t="str">
         <x:v>minecraft:mangrove_log</x:v>
       </x:c>
+      <x:c r="H15" s="8" t="str">
+        <x:v>红树原木</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="str">
+        <x:v>minecraft:mangrove_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
       <x:c r="A16" s="12" t="str">
@@ -10477,6 +12758,15 @@
       <x:c r="G16" s="12" t="str">
         <x:v>minecraft:crimson_stem</x:v>
       </x:c>
+      <x:c r="H16" s="12" t="str">
+        <x:v>绯红菌柄</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="str">
+        <x:v>minecraft:crimson_stem</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
       <x:c r="A17" s="8" t="str">
@@ -10500,6 +12790,15 @@
       <x:c r="G17" s="8" t="str">
         <x:v>minecraft:warped_stem</x:v>
       </x:c>
+      <x:c r="H17" s="8" t="str">
+        <x:v>诡异菌柄</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="8" t="str">
+        <x:v>minecraft:warped_stem</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
       <x:c r="A18" s="12" t="str">
@@ -10523,6 +12822,15 @@
       <x:c r="G18" s="12" t="str">
         <x:v>minecraft:bamboo</x:v>
       </x:c>
+      <x:c r="H18" s="12" t="str">
+        <x:v>竹子</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="str">
+        <x:v>minecraft:bamboo</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
       <x:c r="A19" s="8" t="str">
@@ -10546,6 +12854,15 @@
       <x:c r="G19" s="8" t="str">
         <x:v>minecraft:cobblestone</x:v>
       </x:c>
+      <x:c r="H19" s="8" t="str">
+        <x:v>圆石</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="8" t="str">
+        <x:v>minecraft:cobblestone</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
       <x:c r="A20" s="12" t="str">
@@ -10569,6 +12886,15 @@
       <x:c r="G20" s="12" t="str">
         <x:v>minecraft:stone</x:v>
       </x:c>
+      <x:c r="H20" s="12" t="str">
+        <x:v>石头</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="str">
+        <x:v>minecraft:stone</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
       <x:c r="A21" s="8" t="str">
@@ -10592,6 +12918,15 @@
       <x:c r="G21" s="8" t="str">
         <x:v>minecraft:granite</x:v>
       </x:c>
+      <x:c r="H21" s="8" t="str">
+        <x:v>花岗岩</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="8" t="str">
+        <x:v>minecraft:granite</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
       <x:c r="A22" s="12" t="str">
@@ -10615,6 +12950,15 @@
       <x:c r="G22" s="12" t="str">
         <x:v>minecraft:diorite</x:v>
       </x:c>
+      <x:c r="H22" s="12" t="str">
+        <x:v>闪长岩</x:v>
+      </x:c>
+      <x:c r="I22" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="str">
+        <x:v>minecraft:diorite</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
       <x:c r="A23" s="8" t="str">
@@ -10638,6 +12982,15 @@
       <x:c r="G23" s="8" t="str">
         <x:v>minecraft:andesite</x:v>
       </x:c>
+      <x:c r="H23" s="8" t="str">
+        <x:v>安山岩</x:v>
+      </x:c>
+      <x:c r="I23" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="8" t="str">
+        <x:v>minecraft:andesite</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
       <x:c r="A24" s="12" t="str">
@@ -10661,6 +13014,15 @@
       <x:c r="G24" s="12" t="str">
         <x:v>minecraft:tuff</x:v>
       </x:c>
+      <x:c r="H24" s="12" t="str">
+        <x:v>凝灰岩</x:v>
+      </x:c>
+      <x:c r="I24" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="str">
+        <x:v>minecraft:tuff</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
       <x:c r="A25" s="8" t="str">
@@ -10684,6 +13046,15 @@
       <x:c r="G25" s="8" t="str">
         <x:v>minecraft:cobbled_deepslate</x:v>
       </x:c>
+      <x:c r="H25" s="8" t="str">
+        <x:v>深板岩圆石</x:v>
+      </x:c>
+      <x:c r="I25" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="8" t="str">
+        <x:v>minecraft:cobbled_deepslate</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="12" t="str">
@@ -10707,6 +13078,15 @@
       <x:c r="G26" s="12" t="str">
         <x:v>minecraft:deepslate</x:v>
       </x:c>
+      <x:c r="H26" s="12" t="str">
+        <x:v>深板岩</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="str">
+        <x:v>minecraft:deepslate</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
       <x:c r="A27" s="8" t="str">
@@ -10730,6 +13110,15 @@
       <x:c r="G27" s="8" t="str">
         <x:v>minecraft:basalt</x:v>
       </x:c>
+      <x:c r="H27" s="8" t="str">
+        <x:v>玄武岩</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="8" t="str">
+        <x:v>minecraft:basalt</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
       <x:c r="A28" s="12" t="str">
@@ -10753,6 +13142,15 @@
       <x:c r="G28" s="12" t="str">
         <x:v>minecraft:blackstone</x:v>
       </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>黑石</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" s="12" t="str">
+        <x:v>minecraft:blackstone</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
       <x:c r="A29" s="8" t="str">
@@ -10776,6 +13174,15 @@
       <x:c r="G29" s="8" t="str">
         <x:v>minecraft:netherrack</x:v>
       </x:c>
+      <x:c r="H29" s="8" t="str">
+        <x:v>下界岩</x:v>
+      </x:c>
+      <x:c r="I29" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" s="8" t="str">
+        <x:v>minecraft:netherrack</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
       <x:c r="A30" s="12" t="str">
@@ -10799,6 +13206,15 @@
       <x:c r="G30" s="12" t="str">
         <x:v>minecraft:end_stone</x:v>
       </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>末地石</x:v>
+      </x:c>
+      <x:c r="I30" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="str">
+        <x:v>minecraft:end_stone</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="8" t="str">
@@ -10822,6 +13238,15 @@
       <x:c r="G31" s="8" t="str">
         <x:v>minecraft:soul_sand</x:v>
       </x:c>
+      <x:c r="H31" s="8" t="str">
+        <x:v>灵魂沙</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" s="8" t="str">
+        <x:v>minecraft:soul_sand</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
       <x:c r="A32" s="12" t="str">
@@ -10845,6 +13270,15 @@
       <x:c r="G32" s="12" t="str">
         <x:v>minecraft:soul_soil</x:v>
       </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>灵魂土</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J32" s="12" t="str">
+        <x:v>minecraft:soul_soil</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="8" t="str">
@@ -10868,6 +13302,15 @@
       <x:c r="G33" s="8" t="str">
         <x:v>minecraft:sand</x:v>
       </x:c>
+      <x:c r="H33" s="8" t="str">
+        <x:v>沙子</x:v>
+      </x:c>
+      <x:c r="I33" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J33" s="8" t="str">
+        <x:v>minecraft:sand</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
       <x:c r="A34" s="12" t="str">
@@ -10891,6 +13334,15 @@
       <x:c r="G34" s="12" t="str">
         <x:v>minecraft:red_sand</x:v>
       </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>红沙</x:v>
+      </x:c>
+      <x:c r="I34" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="str">
+        <x:v>minecraft:red_sand</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
       <x:c r="A35" s="8" t="str">
@@ -10914,6 +13366,15 @@
       <x:c r="G35" s="8" t="str">
         <x:v>minecraft:dirt</x:v>
       </x:c>
+      <x:c r="H35" s="8" t="str">
+        <x:v>泥土</x:v>
+      </x:c>
+      <x:c r="I35" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J35" s="8" t="str">
+        <x:v>minecraft:dirt</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="12" t="str">
@@ -10937,6 +13398,15 @@
       <x:c r="G36" s="12" t="str">
         <x:v>minecraft:grass_block</x:v>
       </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>草方块</x:v>
+      </x:c>
+      <x:c r="I36" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J36" s="12" t="str">
+        <x:v>minecraft:grass_block</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
       <x:c r="A37" s="8" t="str">
@@ -10960,6 +13430,15 @@
       <x:c r="G37" s="8" t="str">
         <x:v>minecraft:coarse_dirt</x:v>
       </x:c>
+      <x:c r="H37" s="8" t="str">
+        <x:v>砂土</x:v>
+      </x:c>
+      <x:c r="I37" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J37" s="8" t="str">
+        <x:v>minecraft:coarse_dirt</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
       <x:c r="A38" s="12" t="str">
@@ -10983,6 +13462,15 @@
       <x:c r="G38" s="12" t="str">
         <x:v>minecraft:mud</x:v>
       </x:c>
+      <x:c r="H38" s="12" t="str">
+        <x:v>泥巴</x:v>
+      </x:c>
+      <x:c r="I38" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J38" s="12" t="str">
+        <x:v>minecraft:mud</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
       <x:c r="A39" s="8" t="str">
@@ -11006,6 +13494,15 @@
       <x:c r="G39" s="8" t="str">
         <x:v>minecraft:gravel</x:v>
       </x:c>
+      <x:c r="H39" s="8" t="str">
+        <x:v>沙砾</x:v>
+      </x:c>
+      <x:c r="I39" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J39" s="8" t="str">
+        <x:v>minecraft:gravel</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
       <x:c r="A40" s="12" t="str">
@@ -11029,6 +13526,15 @@
       <x:c r="G40" s="12" t="str">
         <x:v>minecraft:podzol</x:v>
       </x:c>
+      <x:c r="H40" s="12" t="str">
+        <x:v>灰化土</x:v>
+      </x:c>
+      <x:c r="I40" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="str">
+        <x:v>minecraft:podzol</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
       <x:c r="A41" s="8" t="str">
@@ -11052,6 +13558,15 @@
       <x:c r="G41" s="8" t="str">
         <x:v>minecraft:moss_block</x:v>
       </x:c>
+      <x:c r="H41" s="8" t="str">
+        <x:v>苔藓块</x:v>
+      </x:c>
+      <x:c r="I41" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J41" s="8" t="str">
+        <x:v>minecraft:moss_block</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
       <x:c r="A42" s="12" t="str">
@@ -11075,6 +13590,15 @@
       <x:c r="G42" s="12" t="str">
         <x:v>minecraft:clay_ball</x:v>
       </x:c>
+      <x:c r="H42" s="12" t="str">
+        <x:v>黏土球</x:v>
+      </x:c>
+      <x:c r="I42" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J42" s="12" t="str">
+        <x:v>minecraft:clay_ball</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
       <x:c r="A43" s="8" t="str">
@@ -11098,6 +13622,15 @@
       <x:c r="G43" s="8" t="str">
         <x:v>minecraft:snowball</x:v>
       </x:c>
+      <x:c r="H43" s="8" t="str">
+        <x:v>雪球</x:v>
+      </x:c>
+      <x:c r="I43" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J43" s="8" t="str">
+        <x:v>minecraft:snowball</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
       <x:c r="A44" s="12" t="str">
@@ -11121,6 +13654,15 @@
       <x:c r="G44" s="12" t="str">
         <x:v>minecraft:ice</x:v>
       </x:c>
+      <x:c r="H44" s="12" t="str">
+        <x:v>冰</x:v>
+      </x:c>
+      <x:c r="I44" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J44" s="12" t="str">
+        <x:v>minecraft:ice</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
       <x:c r="A45" s="8" t="str">
@@ -11144,6 +13686,15 @@
       <x:c r="G45" s="8" t="str">
         <x:v>minecraft:pointed_dripstone</x:v>
       </x:c>
+      <x:c r="H45" s="8" t="str">
+        <x:v>滴水石锥</x:v>
+      </x:c>
+      <x:c r="I45" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J45" s="8" t="str">
+        <x:v>minecraft:pointed_dripstone</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
       <x:c r="A46" s="12" t="str">
@@ -11167,6 +13718,15 @@
       <x:c r="G46" s="12" t="str">
         <x:v>minecraft:poplar_log</x:v>
       </x:c>
+      <x:c r="H46" s="12" t="str">
+        <x:v>杨木原木</x:v>
+      </x:c>
+      <x:c r="I46" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J46" s="12" t="str">
+        <x:v>minecraft:poplar_log</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
       <x:c r="A47" s="8" t="str">
@@ -11190,6 +13750,15 @@
       <x:c r="G47" s="8" t="str">
         <x:v>minecraft:oak_sapling</x:v>
       </x:c>
+      <x:c r="H47" s="8" t="str">
+        <x:v>橡树树苗</x:v>
+      </x:c>
+      <x:c r="I47" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J47" s="8" t="str">
+        <x:v>minecraft:oak_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
       <x:c r="A48" s="12" t="str">
@@ -11213,6 +13782,15 @@
       <x:c r="G48" s="12" t="str">
         <x:v>minecraft:oak_leaves</x:v>
       </x:c>
+      <x:c r="H48" s="12" t="str">
+        <x:v>橡树树叶</x:v>
+      </x:c>
+      <x:c r="I48" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J48" s="12" t="str">
+        <x:v>minecraft:oak_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
       <x:c r="A49" s="8" t="str">
@@ -11236,6 +13814,15 @@
       <x:c r="G49" s="8" t="str">
         <x:v>minecraft:spruce_sapling</x:v>
       </x:c>
+      <x:c r="H49" s="8" t="str">
+        <x:v>云杉树苗</x:v>
+      </x:c>
+      <x:c r="I49" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J49" s="8" t="str">
+        <x:v>minecraft:spruce_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
       <x:c r="A50" s="12" t="str">
@@ -11259,6 +13846,15 @@
       <x:c r="G50" s="12" t="str">
         <x:v>minecraft:spruce_leaves</x:v>
       </x:c>
+      <x:c r="H50" s="12" t="str">
+        <x:v>云杉树叶</x:v>
+      </x:c>
+      <x:c r="I50" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50" s="12" t="str">
+        <x:v>minecraft:spruce_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
       <x:c r="A51" s="8" t="str">
@@ -11282,6 +13878,15 @@
       <x:c r="G51" s="8" t="str">
         <x:v>minecraft:birch_sapling</x:v>
       </x:c>
+      <x:c r="H51" s="8" t="str">
+        <x:v>白桦树苗</x:v>
+      </x:c>
+      <x:c r="I51" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J51" s="8" t="str">
+        <x:v>minecraft:birch_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
       <x:c r="A52" s="12" t="str">
@@ -11305,6 +13910,15 @@
       <x:c r="G52" s="12" t="str">
         <x:v>minecraft:birch_leaves</x:v>
       </x:c>
+      <x:c r="H52" s="12" t="str">
+        <x:v>白桦树叶</x:v>
+      </x:c>
+      <x:c r="I52" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J52" s="12" t="str">
+        <x:v>minecraft:birch_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
       <x:c r="A53" s="8" t="str">
@@ -11328,6 +13942,15 @@
       <x:c r="G53" s="8" t="str">
         <x:v>minecraft:jungle_sapling</x:v>
       </x:c>
+      <x:c r="H53" s="8" t="str">
+        <x:v>丛林树苗</x:v>
+      </x:c>
+      <x:c r="I53" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J53" s="8" t="str">
+        <x:v>minecraft:jungle_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
       <x:c r="A54" s="12" t="str">
@@ -11351,6 +13974,15 @@
       <x:c r="G54" s="12" t="str">
         <x:v>minecraft:jungle_leaves</x:v>
       </x:c>
+      <x:c r="H54" s="12" t="str">
+        <x:v>丛林树叶</x:v>
+      </x:c>
+      <x:c r="I54" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" s="12" t="str">
+        <x:v>minecraft:jungle_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
       <x:c r="A55" s="8" t="str">
@@ -11374,6 +14006,15 @@
       <x:c r="G55" s="8" t="str">
         <x:v>minecraft:acacia_sapling</x:v>
       </x:c>
+      <x:c r="H55" s="8" t="str">
+        <x:v>金合欢树苗</x:v>
+      </x:c>
+      <x:c r="I55" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" s="8" t="str">
+        <x:v>minecraft:acacia_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
       <x:c r="A56" s="12" t="str">
@@ -11397,6 +14038,15 @@
       <x:c r="G56" s="12" t="str">
         <x:v>minecraft:acacia_leaves</x:v>
       </x:c>
+      <x:c r="H56" s="12" t="str">
+        <x:v>金合欢树叶</x:v>
+      </x:c>
+      <x:c r="I56" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J56" s="12" t="str">
+        <x:v>minecraft:acacia_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
       <x:c r="A57" s="8" t="str">
@@ -11420,6 +14070,15 @@
       <x:c r="G57" s="8" t="str">
         <x:v>minecraft:dark_oak_sapling</x:v>
       </x:c>
+      <x:c r="H57" s="8" t="str">
+        <x:v>深色橡树树苗</x:v>
+      </x:c>
+      <x:c r="I57" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J57" s="8" t="str">
+        <x:v>minecraft:dark_oak_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
       <x:c r="A58" s="12" t="str">
@@ -11443,6 +14102,15 @@
       <x:c r="G58" s="12" t="str">
         <x:v>minecraft:dark_oak_leaves</x:v>
       </x:c>
+      <x:c r="H58" s="12" t="str">
+        <x:v>深色橡树树叶</x:v>
+      </x:c>
+      <x:c r="I58" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J58" s="12" t="str">
+        <x:v>minecraft:dark_oak_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
       <x:c r="A59" s="8" t="str">
@@ -11466,6 +14134,15 @@
       <x:c r="G59" s="8" t="str">
         <x:v>minecraft:cherry_sapling</x:v>
       </x:c>
+      <x:c r="H59" s="8" t="str">
+        <x:v>樱花树苗</x:v>
+      </x:c>
+      <x:c r="I59" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J59" s="8" t="str">
+        <x:v>minecraft:cherry_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
       <x:c r="A60" s="12" t="str">
@@ -11489,6 +14166,15 @@
       <x:c r="G60" s="12" t="str">
         <x:v>minecraft:cherry_leaves</x:v>
       </x:c>
+      <x:c r="H60" s="12" t="str">
+        <x:v>樱花树叶</x:v>
+      </x:c>
+      <x:c r="I60" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J60" s="12" t="str">
+        <x:v>minecraft:cherry_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
       <x:c r="A61" s="8" t="str">
@@ -11512,6 +14198,15 @@
       <x:c r="G61" s="8" t="str">
         <x:v>minecraft:pale_oak_sapling</x:v>
       </x:c>
+      <x:c r="H61" s="8" t="str">
+        <x:v>苍白橡树树苗</x:v>
+      </x:c>
+      <x:c r="I61" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J61" s="8" t="str">
+        <x:v>minecraft:pale_oak_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
       <x:c r="A62" s="12" t="str">
@@ -11535,6 +14230,15 @@
       <x:c r="G62" s="12" t="str">
         <x:v>minecraft:pale_oak_leaves</x:v>
       </x:c>
+      <x:c r="H62" s="12" t="str">
+        <x:v>苍白橡树树叶</x:v>
+      </x:c>
+      <x:c r="I62" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J62" s="12" t="str">
+        <x:v>minecraft:pale_oak_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
       <x:c r="A63" s="8" t="str">
@@ -11558,6 +14262,15 @@
       <x:c r="G63" s="8" t="str">
         <x:v>minecraft:mangrove_propagule</x:v>
       </x:c>
+      <x:c r="H63" s="8" t="str">
+        <x:v>红树胎生苗</x:v>
+      </x:c>
+      <x:c r="I63" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J63" s="8" t="str">
+        <x:v>minecraft:mangrove_propagule</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
       <x:c r="A64" s="12" t="str">
@@ -11581,6 +14294,15 @@
       <x:c r="G64" s="12" t="str">
         <x:v>minecraft:mangrove_leaves</x:v>
       </x:c>
+      <x:c r="H64" s="12" t="str">
+        <x:v>红树树叶</x:v>
+      </x:c>
+      <x:c r="I64" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J64" s="12" t="str">
+        <x:v>minecraft:mangrove_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
       <x:c r="A65" s="8" t="str">
@@ -11604,6 +14326,15 @@
       <x:c r="G65" s="8" t="str">
         <x:v>minecraft:poplar_sapling</x:v>
       </x:c>
+      <x:c r="H65" s="8" t="str">
+        <x:v>杨树树苗</x:v>
+      </x:c>
+      <x:c r="I65" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J65" s="8" t="str">
+        <x:v>minecraft:poplar_sapling</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
       <x:c r="A66" s="12" t="str">
@@ -11627,6 +14358,15 @@
       <x:c r="G66" s="12" t="str">
         <x:v>minecraft:orange_poplar_leaves</x:v>
       </x:c>
+      <x:c r="H66" s="12" t="str">
+        <x:v>橙色杨树树叶</x:v>
+      </x:c>
+      <x:c r="I66" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J66" s="12" t="str">
+        <x:v>minecraft:orange_poplar_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
       <x:c r="A67" s="8" t="str">
@@ -11650,6 +14390,15 @@
       <x:c r="G67" s="8" t="str">
         <x:v>minecraft:red_poplar_leaves</x:v>
       </x:c>
+      <x:c r="H67" s="8" t="str">
+        <x:v>红色杨树树叶</x:v>
+      </x:c>
+      <x:c r="I67" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J67" s="8" t="str">
+        <x:v>minecraft:red_poplar_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
       <x:c r="A68" s="12" t="str">
@@ -11673,6 +14422,15 @@
       <x:c r="G68" s="12" t="str">
         <x:v>minecraft:yellow_poplar_leaves</x:v>
       </x:c>
+      <x:c r="H68" s="12" t="str">
+        <x:v>黄色杨树树叶</x:v>
+      </x:c>
+      <x:c r="I68" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J68" s="12" t="str">
+        <x:v>minecraft:yellow_poplar_leaves</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
       <x:c r="A69" s="8" t="str">
@@ -11696,6 +14454,15 @@
       <x:c r="G69" s="8" t="str">
         <x:v>minecraft:vine</x:v>
       </x:c>
+      <x:c r="H69" s="8" t="str">
+        <x:v>藤蔓</x:v>
+      </x:c>
+      <x:c r="I69" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J69" s="8" t="str">
+        <x:v>minecraft:vine</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
       <x:c r="A70" s="12" t="str">
@@ -11719,6 +14486,15 @@
       <x:c r="G70" s="12" t="str">
         <x:v>minecraft:weeping_vines</x:v>
       </x:c>
+      <x:c r="H70" s="12" t="str">
+        <x:v>垂泪藤</x:v>
+      </x:c>
+      <x:c r="I70" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J70" s="12" t="str">
+        <x:v>minecraft:weeping_vines</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
       <x:c r="A71" s="8" t="str">
@@ -11742,6 +14518,15 @@
       <x:c r="G71" s="8" t="str">
         <x:v>minecraft:twisting_vines</x:v>
       </x:c>
+      <x:c r="H71" s="8" t="str">
+        <x:v>缠怨藤</x:v>
+      </x:c>
+      <x:c r="I71" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J71" s="8" t="str">
+        <x:v>minecraft:twisting_vines</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="28" customHeight="1">
       <x:c r="A72" s="12" t="str">
@@ -11765,6 +14550,15 @@
       <x:c r="G72" s="12" t="str">
         <x:v>minecraft:sugar_cane</x:v>
       </x:c>
+      <x:c r="H72" s="12" t="str">
+        <x:v>甘蔗</x:v>
+      </x:c>
+      <x:c r="I72" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J72" s="12" t="str">
+        <x:v>minecraft:sugar_cane</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="28" customHeight="1">
       <x:c r="A73" s="8" t="str">
@@ -11788,6 +14582,15 @@
       <x:c r="G73" s="8" t="str">
         <x:v>minecraft:cactus</x:v>
       </x:c>
+      <x:c r="H73" s="8" t="str">
+        <x:v>仙人掌</x:v>
+      </x:c>
+      <x:c r="I73" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J73" s="8" t="str">
+        <x:v>minecraft:cactus</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="28" customHeight="1">
       <x:c r="A74" s="12" t="str">
@@ -11811,6 +14614,15 @@
       <x:c r="G74" s="12" t="str">
         <x:v>minecraft:kelp</x:v>
       </x:c>
+      <x:c r="H74" s="12" t="str">
+        <x:v>海带</x:v>
+      </x:c>
+      <x:c r="I74" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J74" s="12" t="str">
+        <x:v>minecraft:kelp</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="28" customHeight="1">
       <x:c r="A75" s="8" t="str">
@@ -11834,6 +14646,15 @@
       <x:c r="G75" s="8" t="str">
         <x:v>minecraft:leaf_litter</x:v>
       </x:c>
+      <x:c r="H75" s="8" t="str">
+        <x:v>枯叶堆</x:v>
+      </x:c>
+      <x:c r="I75" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J75" s="8" t="str">
+        <x:v>minecraft:leaf_litter</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="28" customHeight="1">
       <x:c r="A76" s="12" t="str">
@@ -11857,6 +14678,15 @@
       <x:c r="G76" s="12" t="str">
         <x:v>minecraft:seagrass</x:v>
       </x:c>
+      <x:c r="H76" s="12" t="str">
+        <x:v>海草</x:v>
+      </x:c>
+      <x:c r="I76" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J76" s="12" t="str">
+        <x:v>minecraft:seagrass</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="28" customHeight="1">
       <x:c r="A77" s="8" t="str">
@@ -11880,6 +14710,15 @@
       <x:c r="G77" s="8" t="str">
         <x:v>minecraft:lily_pad</x:v>
       </x:c>
+      <x:c r="H77" s="8" t="str">
+        <x:v>睡莲</x:v>
+      </x:c>
+      <x:c r="I77" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J77" s="8" t="str">
+        <x:v>minecraft:lily_pad</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="28" customHeight="1">
       <x:c r="A78" s="12" t="str">
@@ -11903,6 +14742,15 @@
       <x:c r="G78" s="12" t="str">
         <x:v>minecraft:fern</x:v>
       </x:c>
+      <x:c r="H78" s="12" t="str">
+        <x:v>蕨</x:v>
+      </x:c>
+      <x:c r="I78" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J78" s="12" t="str">
+        <x:v>minecraft:fern</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="28" customHeight="1">
       <x:c r="A79" s="8" t="str">
@@ -11926,6 +14774,15 @@
       <x:c r="G79" s="8" t="str">
         <x:v>minecraft:large_fern</x:v>
       </x:c>
+      <x:c r="H79" s="8" t="str">
+        <x:v>大型蕨</x:v>
+      </x:c>
+      <x:c r="I79" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J79" s="8" t="str">
+        <x:v>minecraft:large_fern</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="28" customHeight="1">
       <x:c r="A80" s="12" t="str">
@@ -11949,6 +14806,15 @@
       <x:c r="G80" s="12" t="str">
         <x:v>minecraft:dead_bush</x:v>
       </x:c>
+      <x:c r="H80" s="12" t="str">
+        <x:v>枯萎的灌木</x:v>
+      </x:c>
+      <x:c r="I80" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J80" s="12" t="str">
+        <x:v>minecraft:dead_bush</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="28" customHeight="1">
       <x:c r="A81" s="8" t="str">
@@ -11972,6 +14838,15 @@
       <x:c r="G81" s="8" t="str">
         <x:v>minecraft:short_grass</x:v>
       </x:c>
+      <x:c r="H81" s="8" t="str">
+        <x:v>矮草丛</x:v>
+      </x:c>
+      <x:c r="I81" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J81" s="8" t="str">
+        <x:v>minecraft:short_grass</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="28" customHeight="1">
       <x:c r="A82" s="12" t="str">
@@ -11995,6 +14870,15 @@
       <x:c r="G82" s="12" t="str">
         <x:v>minecraft:tall_grass</x:v>
       </x:c>
+      <x:c r="H82" s="12" t="str">
+        <x:v>高草丛</x:v>
+      </x:c>
+      <x:c r="I82" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J82" s="12" t="str">
+        <x:v>minecraft:tall_grass</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="28" customHeight="1">
       <x:c r="A83" s="8" t="str">
@@ -12018,6 +14902,15 @@
       <x:c r="G83" s="8" t="str">
         <x:v>minecraft:short_dry_grass</x:v>
       </x:c>
+      <x:c r="H83" s="8" t="str">
+        <x:v>矮枯草丛</x:v>
+      </x:c>
+      <x:c r="I83" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J83" s="8" t="str">
+        <x:v>minecraft:short_dry_grass</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="28" customHeight="1">
       <x:c r="A84" s="12" t="str">
@@ -12041,6 +14934,15 @@
       <x:c r="G84" s="12" t="str">
         <x:v>minecraft:tall_dry_grass</x:v>
       </x:c>
+      <x:c r="H84" s="12" t="str">
+        <x:v>高枯草丛</x:v>
+      </x:c>
+      <x:c r="I84" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J84" s="12" t="str">
+        <x:v>minecraft:tall_dry_grass</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="28" customHeight="1">
       <x:c r="A85" s="8" t="str">
@@ -12064,6 +14966,15 @@
       <x:c r="G85" s="8" t="str">
         <x:v>minecraft:dandelion</x:v>
       </x:c>
+      <x:c r="H85" s="8" t="str">
+        <x:v>蒲公英</x:v>
+      </x:c>
+      <x:c r="I85" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J85" s="8" t="str">
+        <x:v>minecraft:dandelion</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="28" customHeight="1">
       <x:c r="A86" s="12" t="str">
@@ -12087,6 +14998,15 @@
       <x:c r="G86" s="12" t="str">
         <x:v>minecraft:poppy</x:v>
       </x:c>
+      <x:c r="H86" s="12" t="str">
+        <x:v>虞美人</x:v>
+      </x:c>
+      <x:c r="I86" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J86" s="12" t="str">
+        <x:v>minecraft:poppy</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="28" customHeight="1">
       <x:c r="A87" s="8" t="str">
@@ -12110,6 +15030,15 @@
       <x:c r="G87" s="8" t="str">
         <x:v>minecraft:blue_orchid</x:v>
       </x:c>
+      <x:c r="H87" s="8" t="str">
+        <x:v>兰花</x:v>
+      </x:c>
+      <x:c r="I87" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J87" s="8" t="str">
+        <x:v>minecraft:blue_orchid</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="28" customHeight="1">
       <x:c r="A88" s="12" t="str">
@@ -12133,6 +15062,15 @@
       <x:c r="G88" s="12" t="str">
         <x:v>minecraft:allium</x:v>
       </x:c>
+      <x:c r="H88" s="12" t="str">
+        <x:v>绒球葱</x:v>
+      </x:c>
+      <x:c r="I88" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J88" s="12" t="str">
+        <x:v>minecraft:allium</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="28" customHeight="1">
       <x:c r="A89" s="8" t="str">
@@ -12156,6 +15094,15 @@
       <x:c r="G89" s="8" t="str">
         <x:v>minecraft:azure_bluet</x:v>
       </x:c>
+      <x:c r="H89" s="8" t="str">
+        <x:v>蓝花美耳草</x:v>
+      </x:c>
+      <x:c r="I89" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J89" s="8" t="str">
+        <x:v>minecraft:azure_bluet</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="28" customHeight="1">
       <x:c r="A90" s="12" t="str">
@@ -12179,6 +15126,15 @@
       <x:c r="G90" s="12" t="str">
         <x:v>minecraft:red_tulip</x:v>
       </x:c>
+      <x:c r="H90" s="12" t="str">
+        <x:v>红色郁金香</x:v>
+      </x:c>
+      <x:c r="I90" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J90" s="12" t="str">
+        <x:v>minecraft:red_tulip</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="28" customHeight="1">
       <x:c r="A91" s="8" t="str">
@@ -12202,6 +15158,15 @@
       <x:c r="G91" s="8" t="str">
         <x:v>minecraft:orange_tulip</x:v>
       </x:c>
+      <x:c r="H91" s="8" t="str">
+        <x:v>橙色郁金香</x:v>
+      </x:c>
+      <x:c r="I91" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J91" s="8" t="str">
+        <x:v>minecraft:orange_tulip</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="28" customHeight="1">
       <x:c r="A92" s="12" t="str">
@@ -12225,6 +15190,15 @@
       <x:c r="G92" s="12" t="str">
         <x:v>minecraft:white_tulip</x:v>
       </x:c>
+      <x:c r="H92" s="12" t="str">
+        <x:v>白色郁金香</x:v>
+      </x:c>
+      <x:c r="I92" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J92" s="12" t="str">
+        <x:v>minecraft:white_tulip</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="28" customHeight="1">
       <x:c r="A93" s="8" t="str">
@@ -12248,6 +15222,15 @@
       <x:c r="G93" s="8" t="str">
         <x:v>minecraft:pink_tulip</x:v>
       </x:c>
+      <x:c r="H93" s="8" t="str">
+        <x:v>粉红色郁金香</x:v>
+      </x:c>
+      <x:c r="I93" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J93" s="8" t="str">
+        <x:v>minecraft:pink_tulip</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" ht="28" customHeight="1">
       <x:c r="A94" s="12" t="str">
@@ -12271,6 +15254,15 @@
       <x:c r="G94" s="12" t="str">
         <x:v>minecraft:oxeye_daisy</x:v>
       </x:c>
+      <x:c r="H94" s="12" t="str">
+        <x:v>滨菊</x:v>
+      </x:c>
+      <x:c r="I94" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J94" s="12" t="str">
+        <x:v>minecraft:oxeye_daisy</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="28" customHeight="1">
       <x:c r="A95" s="8" t="str">
@@ -12294,6 +15286,15 @@
       <x:c r="G95" s="8" t="str">
         <x:v>minecraft:cornflower</x:v>
       </x:c>
+      <x:c r="H95" s="8" t="str">
+        <x:v>矢车菊</x:v>
+      </x:c>
+      <x:c r="I95" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J95" s="8" t="str">
+        <x:v>minecraft:cornflower</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="28" customHeight="1">
       <x:c r="A96" s="12" t="str">
@@ -12317,6 +15318,15 @@
       <x:c r="G96" s="12" t="str">
         <x:v>minecraft:lily_of_the_valley</x:v>
       </x:c>
+      <x:c r="H96" s="12" t="str">
+        <x:v>铃兰</x:v>
+      </x:c>
+      <x:c r="I96" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J96" s="12" t="str">
+        <x:v>minecraft:lily_of_the_valley</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="28" customHeight="1">
       <x:c r="A97" s="8" t="str">
@@ -12340,6 +15350,15 @@
       <x:c r="G97" s="8" t="str">
         <x:v>minecraft:sunflower</x:v>
       </x:c>
+      <x:c r="H97" s="8" t="str">
+        <x:v>向日葵</x:v>
+      </x:c>
+      <x:c r="I97" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J97" s="8" t="str">
+        <x:v>minecraft:sunflower</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="28" customHeight="1">
       <x:c r="A98" s="12" t="str">
@@ -12363,6 +15382,15 @@
       <x:c r="G98" s="12" t="str">
         <x:v>minecraft:lilac</x:v>
       </x:c>
+      <x:c r="H98" s="12" t="str">
+        <x:v>丁香</x:v>
+      </x:c>
+      <x:c r="I98" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J98" s="12" t="str">
+        <x:v>minecraft:lilac</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="28" customHeight="1">
       <x:c r="A99" s="8" t="str">
@@ -12386,6 +15414,15 @@
       <x:c r="G99" s="8" t="str">
         <x:v>minecraft:rose_bush</x:v>
       </x:c>
+      <x:c r="H99" s="8" t="str">
+        <x:v>玫瑰丛</x:v>
+      </x:c>
+      <x:c r="I99" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J99" s="8" t="str">
+        <x:v>minecraft:rose_bush</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="28" customHeight="1">
       <x:c r="A100" s="12" t="str">
@@ -12409,6 +15446,15 @@
       <x:c r="G100" s="12" t="str">
         <x:v>minecraft:peony</x:v>
       </x:c>
+      <x:c r="H100" s="12" t="str">
+        <x:v>牡丹</x:v>
+      </x:c>
+      <x:c r="I100" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J100" s="12" t="str">
+        <x:v>minecraft:peony</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="28" customHeight="1">
       <x:c r="A101" s="8" t="str">
@@ -12432,6 +15478,15 @@
       <x:c r="G101" s="8" t="str">
         <x:v>minecraft:cactus_flower</x:v>
       </x:c>
+      <x:c r="H101" s="8" t="str">
+        <x:v>仙人掌花</x:v>
+      </x:c>
+      <x:c r="I101" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J101" s="8" t="str">
+        <x:v>minecraft:cactus_flower</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="28" customHeight="1">
       <x:c r="A102" s="12" t="str">
@@ -12455,6 +15510,15 @@
       <x:c r="G102" s="12" t="str">
         <x:v>minecraft:wildflowers</x:v>
       </x:c>
+      <x:c r="H102" s="12" t="str">
+        <x:v>野花簇</x:v>
+      </x:c>
+      <x:c r="I102" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J102" s="12" t="str">
+        <x:v>minecraft:wildflowers</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="28" customHeight="1">
       <x:c r="A103" s="8" t="str">
@@ -12478,6 +15542,15 @@
       <x:c r="G103" s="8" t="str">
         <x:v>minecraft:pink_petals</x:v>
       </x:c>
+      <x:c r="H103" s="8" t="str">
+        <x:v>粉红色花簇</x:v>
+      </x:c>
+      <x:c r="I103" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J103" s="8" t="str">
+        <x:v>minecraft:pink_petals</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="28" customHeight="1">
       <x:c r="A104" s="12" t="str">
@@ -12501,6 +15574,15 @@
       <x:c r="G104" s="12" t="str">
         <x:v>minecraft:red_mushroom</x:v>
       </x:c>
+      <x:c r="H104" s="12" t="str">
+        <x:v>红色蘑菇</x:v>
+      </x:c>
+      <x:c r="I104" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J104" s="12" t="str">
+        <x:v>minecraft:red_mushroom</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="28" customHeight="1">
       <x:c r="A105" s="8" t="str">
@@ -12524,6 +15606,15 @@
       <x:c r="G105" s="8" t="str">
         <x:v>minecraft:brown_mushroom</x:v>
       </x:c>
+      <x:c r="H105" s="8" t="str">
+        <x:v>棕色蘑菇</x:v>
+      </x:c>
+      <x:c r="I105" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J105" s="8" t="str">
+        <x:v>minecraft:brown_mushroom</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="28" customHeight="1">
       <x:c r="A106" s="12" t="str">
@@ -12547,6 +15638,15 @@
       <x:c r="G106" s="12" t="str">
         <x:v>minecraft:crimson_fungus</x:v>
       </x:c>
+      <x:c r="H106" s="12" t="str">
+        <x:v>绯红菌</x:v>
+      </x:c>
+      <x:c r="I106" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J106" s="12" t="str">
+        <x:v>minecraft:crimson_fungus</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="28" customHeight="1">
       <x:c r="A107" s="8" t="str">
@@ -12570,6 +15670,15 @@
       <x:c r="G107" s="8" t="str">
         <x:v>minecraft:warped_fungus</x:v>
       </x:c>
+      <x:c r="H107" s="8" t="str">
+        <x:v>诡异菌</x:v>
+      </x:c>
+      <x:c r="I107" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J107" s="8" t="str">
+        <x:v>minecraft:warped_fungus</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="28" customHeight="1">
       <x:c r="A108" s="12" t="str">
@@ -12593,6 +15702,15 @@
       <x:c r="G108" s="12" t="str">
         <x:v>minecraft:crimson_roots</x:v>
       </x:c>
+      <x:c r="H108" s="12" t="str">
+        <x:v>绯红菌索</x:v>
+      </x:c>
+      <x:c r="I108" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J108" s="12" t="str">
+        <x:v>minecraft:crimson_roots</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="28" customHeight="1">
       <x:c r="A109" s="8" t="str">
@@ -12616,6 +15734,15 @@
       <x:c r="G109" s="8" t="str">
         <x:v>minecraft:warped_roots</x:v>
       </x:c>
+      <x:c r="H109" s="8" t="str">
+        <x:v>诡异菌索</x:v>
+      </x:c>
+      <x:c r="I109" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J109" s="8" t="str">
+        <x:v>minecraft:warped_roots</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="28" customHeight="1">
       <x:c r="A110" s="12" t="str">
@@ -12639,6 +15766,15 @@
       <x:c r="G110" s="12" t="str">
         <x:v>minecraft:nether_sprouts</x:v>
       </x:c>
+      <x:c r="H110" s="12" t="str">
+        <x:v>下界苗</x:v>
+      </x:c>
+      <x:c r="I110" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J110" s="12" t="str">
+        <x:v>minecraft:nether_sprouts</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="28" customHeight="1">
       <x:c r="A111" s="8" t="str">
@@ -12662,11 +15798,20 @@
       <x:c r="G111" s="8" t="str">
         <x:v>minecraft:calcite</x:v>
       </x:c>
+      <x:c r="H111" s="8" t="str">
+        <x:v>方解石</x:v>
+      </x:c>
+      <x:c r="I111" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J111" s="8" t="str">
+        <x:v>minecraft:calcite</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33bb2350ecee4d07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8d6ccbabfaf4a72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12889,7 +16034,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaece4aefc274b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66639487d8f7455a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a0f354-50a1-7850-9a3e-c4f75b90728b/ConvertTable配方.xlsx
+++ b/outputs/01a0f354-50a1-7850-9a3e-c4f75b90728b/ConvertTable配方.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方总览" sheetId="1" r:id="R2d0bef3ee8964282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通转换" sheetId="2" r:id="Raf842d6e706e4963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幽匿进阶" sheetId="3" r:id="Ra15cc80006f947f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触媒增殖" sheetId="4" r:id="Rb60f3c7768c94b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方块合成" sheetId="5" r:id="R4b6fe9a8422e494c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配方总览" sheetId="1" r:id="Ree8ab3f06a1b424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通转换" sheetId="2" r:id="R718c3e7ff4b24e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幽匿进阶" sheetId="3" r:id="R10ec347b90614a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触媒增殖" sheetId="4" r:id="Ra6e88f23d53641dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方块合成" sheetId="5" r:id="R3c069f3f66934ad1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -544,7 +544,7 @@
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="35" t="str">
-        <x:v>ConvertTable v0.3.1 配方</x:v>
+        <x:v>ConvertTable v0.3.2 配方</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -5697,7 +5697,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab708fb60ef44d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3b32f05cd754037"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12361,7 +12361,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re20cd67569ea4397"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e601eb72c4145e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12408,7 +12408,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>放入触媒和一件目标物品作源本，两者都不消耗；每次产出 1 件。小/中/大/成熟晶芽自然内涵量为 16/64、8/64、4/64、1/64；未成熟晶芽每秒抽取上限 1/64，方解石为 2/64。产速 = 分配的生长因子/秒 ÷ 单件成本。</x:v>
+        <x:v>放入触媒和一件目标物品作源本，两者都不消耗；每次产出 1 件。小/中/大/成熟晶芽自然内涵量为 16/1000、8/1000、4/1000、1/1000；每个未成熟晶芽基础供给 1/1000 因子/秒；每块方解石再加 1/1000，可叠加。产速 = 分配的生长因子/秒 ÷ 单件成本。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -15811,7 +15811,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8d6ccbabfaf4a72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb087b40d464044da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16034,7 +16034,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66639487d8f7455a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17ac34bf564b400e"/>
   </x:tableParts>
 </x:worksheet>
 </file>